--- a/output/citadele_reviews_latest.xlsx
+++ b/output/citadele_reviews_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Reviews'!$A$1:$K$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Reviews'!$A$1:$K$204</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K205"/>
+  <dimension ref="A1:K204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3511,67 +3511,14 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Slēpj lietotnes kļūdas zem "slepenības" plīvura</t>
+          <t>Nedarbojas korekti aplikācija</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>Jaunākajos atjauninājumos tika sabojāta Apple Shortcuts (App Intents) integrācija. Uz tehnisku jautājumu ar pierādījumiem atbalsta dienests pēc 2 nedēļām atbildēja, ka informācija par to, vai funkcijas nedarbošanās ir kļūda (bugs), ir "iekšējs tehniskais lēmums, ko klientiem neatklāj". Tā vietā, lai labotu kļūdas, banka tās slēpj aiz atrunām.</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>Igbu8</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>46.4</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-05T09:53:47-07:00</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>14391669011</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>https://itunes.apple.com/lv/reviews/id353310269</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Latvia</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>lv</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>Nedarbojas korekti aplikācija</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>Jau divas nedēļas nevaru apskatīties vai nu privāto vai uzņēmuma kontu, caur aplikāciju. Web versija visu var redzēt, bet tā mani tracina, jo nav labi pārskatāma.
 Aplikāciju esmu izdzēsusi jau 4x un telefonu restartējusi katru reizi. 
@@ -3580,9 +3527,62 @@
 Salabojojiet beidzot savu aplikāciju!!!!!</t>
         </is>
       </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Leastar2289</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>46.4</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13T12:01:12-07:00</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>14299202795</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id329005494</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Parslegsana starp kontiem</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Jau nedēļu aplikācija nestrādā ! Ne no datora nevar Ienākt konta ne no telefona. Lai dabūt piekļuvi vaj dokumentus jascane, va dzēst un lejupielādēt no jauna.</t>
+        </is>
+      </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Leastar2289</t>
+          <t>Cienījamais</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -3592,17 +3592,17 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13T12:01:12-07:00</t>
+          <t>2026-06-30T06:27:45-07:00</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>14299202795</t>
+          <t>14245121606</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id329005494</t>
+          <t>https://itunes.apple.com/lv/reviews/id1939142419</t>
         </is>
       </c>
       <c r="K59" s="2" t="n">
@@ -3625,37 +3625,37 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Parslegsana starp kontiem</t>
+          <t>Requires canera access</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Jau nedēļu aplikācija nestrādā ! Ne no datora nevar Ienākt konta ne no telefona. Lai dabūt piekļuvi vaj dokumentus jascane, va dzēst un lejupielādēt no jauna.</t>
+          <t>Requires camera access for face scan despite the customer has other authentication tools.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Cienījamais</t>
+          <t>Oblivious Reawake</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30T06:27:45-07:00</t>
+          <t>2026-06-10T01:16:20-07:00</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>14245121606</t>
+          <t>14165218601</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1939142419</t>
+          <t>https://itunes.apple.com/lv/reviews/id1931282409</t>
         </is>
       </c>
       <c r="K60" s="2" t="n">
@@ -3674,21 +3674,21 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Requires canera access</t>
+          <t>Зависает</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Requires camera access for face scan despite the customer has other authentication tools.</t>
+          <t>Периодически зависает на от какой нибудь страничке приложения. Не понятно как перезапустить. А когда нужно что-то срочно сделать, оплатить это очень мешает.</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Oblivious Reawake</t>
+          <t>Irinaromance</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -3698,17 +3698,17 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10T01:16:20-07:00</t>
+          <t>2026-05-29T02:05:01-07:00</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>14165218601</t>
+          <t>14118721418</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1931282409</t>
+          <t>https://itunes.apple.com/lv/reviews/id1774791733</t>
         </is>
       </c>
       <c r="K61" s="2" t="n">
@@ -3727,21 +3727,21 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Зависает</t>
+          <t>Password</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Периодически зависает на от какой нибудь страничке приложения. Не понятно как перезапустить. А когда нужно что-то срочно сделать, оплатить это очень мешает.</t>
+          <t>Very laggy, i cant make new password</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Irinaromance</t>
+          <t>Hahakdkakw</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -3751,17 +3751,17 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29T02:05:01-07:00</t>
+          <t>2026-05-12T03:07:56-07:00</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>14118721418</t>
+          <t>14055672060</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1774791733</t>
+          <t>https://itunes.apple.com/lv/reviews/id1015219998</t>
         </is>
       </c>
       <c r="K62" s="2" t="n">
@@ -3780,21 +3780,21 @@
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Best</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Very laggy, i cant make new password</t>
+          <t>Best of the Best</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Hahakdkakw</t>
+          <t>AnnaJe</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -3804,17 +3804,17 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12T03:07:56-07:00</t>
+          <t>2026-05-10T09:58:21-07:00</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>14055672060</t>
+          <t>14049672987</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1015219998</t>
+          <t>https://itunes.apple.com/lv/reviews/id374669959</t>
         </is>
       </c>
       <c r="K63" s="2" t="n">
@@ -3833,96 +3833,96 @@
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Best</t>
+          <t>Titulis</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>Best of the Best</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>AnnaJe</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>46.1</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-10T09:58:21-07:00</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>14049672987</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>https://itunes.apple.com/lv/reviews/id374669959</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Latvia</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>lv</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>Titulis</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>Lūdzu, izlabojiet, lai versija priekš iOS16 (iphone8) var lietot Atlikums funkciju..
 Šobrīd vairs tālāk par login logu nevar tikt..
 (iPhone 8/X vēl saņem security updates, bet nevar uz iOS 17 upgradot)</t>
         </is>
       </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>NeviensNekurNekad</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25T17:35:06-07:00</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>13997219931</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id1182576565</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Maksājums</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Ātri un ērti</t>
+        </is>
+      </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>NeviensNekurNekad</t>
+          <t>Nordstock</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>2026-04-25T17:35:06-07:00</t>
+          <t>2026-04-21T00:09:34-07:00</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>13997219931</t>
+          <t>13980784641</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1182576565</t>
+          <t>https://itunes.apple.com/lv/reviews/id474740478</t>
         </is>
       </c>
       <c r="K65" s="2" t="n">
@@ -3945,17 +3945,17 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Maksājums</t>
+          <t>Good ap</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Ātri un ērti</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Nordstock</t>
+          <t>BMX boy673</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -3965,17 +3965,17 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>2026-04-21T00:09:34-07:00</t>
+          <t>2026-04-03T03:53:43-07:00</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>13980784641</t>
+          <t>13917409833</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id474740478</t>
+          <t>https://itunes.apple.com/lv/reviews/id1907543400</t>
         </is>
       </c>
       <c r="K66" s="2" t="n">
@@ -3994,41 +3994,41 @@
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Good ap</t>
+          <t>Izrādās lai piekłūtu kontam ir nepieciešams jaunākās versijas IOS, pārējiem banka telefonā slēgta</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Łoti negorši no CITADELE puses nobloket iespēju ieiet internet bankas aplikacija tikai tāpēc, ka nepatīk programmaturas versija, galīgi nav forši kā klientam pēkšñi attapties, ka pieeja bankai ir ietobežota tikai tāpēc ka nepatīk IOS versija, neko šādu no bankas gan negaidīju !</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>BMX boy673</t>
+          <t>Nonnn. N</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>2026-04-03T03:53:43-07:00</t>
+          <t>2026-02-02T05:59:32-07:00</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>13917409833</t>
+          <t>13704714125</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1907543400</t>
+          <t>https://itunes.apple.com/lv/reviews/id1344867938</t>
         </is>
       </c>
       <c r="K67" s="2" t="n">
@@ -4047,41 +4047,41 @@
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Izrādās lai piekłūtu kontam ir nepieciešams jaunākās versijas IOS, pārējiem banka telefonā slēgta</t>
+          <t>Pro Bank</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>Łoti negorši no CITADELE puses nobloket iespēju ieiet internet bankas aplikacija tikai tāpēc, ka nepatīk programmaturas versija, galīgi nav forši kā klientam pēkšñi attapties, ka pieeja bankai ir ietobežota tikai tāpēc ka nepatīk IOS versija, neko šādu no bankas gan negaidīju !</t>
+          <t>The bank is friendly, the staff are very helpful, and they assisted me a lot when I needed help.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Nonnn. N</t>
+          <t>Chuyên nghiệp Bank</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2026-02-02T05:59:32-07:00</t>
+          <t>2026-01-22T23:54:22-07:00</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>13704714125</t>
+          <t>13665503813</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1344867938</t>
+          <t>https://itunes.apple.com/lv/reviews/id1614644439</t>
         </is>
       </c>
       <c r="K68" s="2" t="n">
@@ -4104,17 +4104,17 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Pro Bank</t>
+          <t>Forša aplikācija</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>The bank is friendly, the staff are very helpful, and they assisted me a lot when I needed help.</t>
+          <t>Lieliska aplikācija, strādā bez problèmām, var piekłūt ar pirkta nospieduma un saņemt notifikācijas par maksājumiem, citām bankām šādas opcijas nevienmēr ir</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Chuyên nghiệp Bank</t>
+          <t>Ine098</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -4124,17 +4124,17 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>2026-01-22T23:54:22-07:00</t>
+          <t>2026-01-15T02:19:42-07:00</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>13665503813</t>
+          <t>13635607369</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1614644439</t>
+          <t>https://itunes.apple.com/lv/reviews/id601426458</t>
         </is>
       </c>
       <c r="K69" s="2" t="n">
@@ -4153,21 +4153,21 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Forša aplikācija</t>
+          <t>Reklāmas aplikācija</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Lieliska aplikācija, strādā bez problèmām, var piekłūt ar pirkta nospieduma un saņemt notifikācijas par maksājumiem, citām bankām šādas opcijas nevienmēr ir</t>
+          <t>Tas ir noragašanas par lietotāju likt sadaļu kur Tev tamborē par “aktualitātēm” t.i. REKLĀMA!!! Pārejas sadaļas var mainīt vietām, bet šo nē. 110% besis par to!</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Ine098</t>
+          <t>ivasap</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -4177,17 +4177,17 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>2026-01-15T02:19:42-07:00</t>
+          <t>2025-12-26T11:39:18-07:00</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>13635607369</t>
+          <t>13558125017</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id601426458</t>
+          <t>https://itunes.apple.com/lv/reviews/id338039968</t>
         </is>
       </c>
       <c r="K70" s="2" t="n">
@@ -4210,37 +4210,37 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Reklāmas aplikācija</t>
+          <t>Forced updates</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Tas ir noragašanas par lietotāju likt sadaļu kur Tev tamborē par “aktualitātēm” t.i. REKLĀMA!!! Pārejas sadaļas var mainīt vietām, bet šo nē. 110% besis par to!</t>
+          <t>Aplikācija vairs nestrādā jo man jāpērk jauns telefons, tā vismaz Citadele banka uzskata :)</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>ivasap</t>
+          <t>HelmutsR</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>2025-12-26T11:39:18-07:00</t>
+          <t>2025-12-01T01:10:43-07:00</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>13558125017</t>
+          <t>13461819713</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id338039968</t>
+          <t>https://itunes.apple.com/lv/reviews/id555983244</t>
         </is>
       </c>
       <c r="K71" s="2" t="n">
@@ -4263,17 +4263,17 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Forced updates</t>
+          <t>Stopped working on my Iphone X ios16. Thats bad service.</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Aplikācija vairs nestrādā jo man jāpērk jauns telefons, tā vismaz Citadele banka uzskata :)</t>
+          <t>Should work as long as I have this phone where app was installed. Bank wants me to buy a new phone. Now I got a new trouble to solve. Mau be time ti change bank?</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>HelmutsR</t>
+          <t>Janis Alnis</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -4283,17 +4283,17 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>2025-12-01T01:10:43-07:00</t>
+          <t>2025-10-11T04:10:17-07:00</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>13461819713</t>
+          <t>13252100973</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id555983244</t>
+          <t>https://itunes.apple.com/lv/reviews/id1040374104</t>
         </is>
       </c>
       <c r="K72" s="2" t="n">
@@ -4312,41 +4312,41 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Stopped working on my Iphone X ios16. Thats bad service.</t>
+          <t>Favorite bank app</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Should work as long as I have this phone where app was installed. Bank wants me to buy a new phone. Now I got a new trouble to solve. Mau be time ti change bank?</t>
+          <t>Very nice banking app and simple to use too. My father has been using it for years, I was only about 11 or 12 years old when he got me my first Citadele credit card:) Since then also my mom started using this app and then my brother, seems like such a simple thing but it makes the transactions so much easier between us. We also really love Citadele rewards, recently I bought a delicious drink using my points, it was deffinetly worth it!😊</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Janis Alnis</t>
+          <t>CarryMilka</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>2025-10-11T04:10:17-07:00</t>
+          <t>2025-10-08T05:48:31-07:00</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>13252100973</t>
+          <t>13239773092</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1040374104</t>
+          <t>https://itunes.apple.com/lv/reviews/id1564549114</t>
         </is>
       </c>
       <c r="K73" s="2" t="n">
@@ -4365,21 +4365,21 @@
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Favorite bank app</t>
+          <t>Ужасное обновление</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>Very nice banking app and simple to use too. My father has been using it for years, I was only about 11 or 12 years old when he got me my first Citadele credit card:) Since then also my mom started using this app and then my brother, seems like such a simple thing but it makes the transactions so much easier between us. We also really love Citadele rewards, recently I bought a delicious drink using my points, it was deffinetly worth it!😊</t>
+          <t>Постоянно глючит и выбрасывает с приложения!</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>CarryMilka</t>
+          <t>IzabelleM0909</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -4389,17 +4389,17 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>2025-10-08T05:48:31-07:00</t>
+          <t>2025-10-07T14:25:11-07:00</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>13239773092</t>
+          <t>13237307199</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1564549114</t>
+          <t>https://itunes.apple.com/lv/reviews/id376387269</t>
         </is>
       </c>
       <c r="K74" s="2" t="n">
@@ -4418,41 +4418,41 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Ужасное обновление</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Постоянно глючит и выбрасывает с приложения!</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>IzabelleM0909</t>
+          <t>VAZaharovs</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>2025-10-07T14:25:11-07:00</t>
+          <t>2025-09-30T00:54:50-07:00</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>13237307199</t>
+          <t>13203622921</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id376387269</t>
+          <t>https://itunes.apple.com/lv/reviews/id1524302955</t>
         </is>
       </c>
       <c r="K75" s="2" t="n">
@@ -4471,21 +4471,21 @@
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>0,01 zvaigzne</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Sliktākā un nepārskatāmā internetbanka un aplikācija salīdzinājumā ar citām LV bankām</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>VAZaharovs</t>
+          <t>Ainars-st</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -4495,17 +4495,17 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>2025-09-30T00:54:50-07:00</t>
+          <t>2025-09-26T08:13:49-07:00</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>13203622921</t>
+          <t>13187722367</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1524302955</t>
+          <t>https://itunes.apple.com/lv/reviews/id302645165</t>
         </is>
       </c>
       <c r="K76" s="2" t="n">
@@ -4528,37 +4528,37 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>0,01 zvaigzne</t>
+          <t>Bad service</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Sliktākā un nepārskatāmā internetbanka un aplikācija salīdzinājumā ar citām LV bankām</t>
+          <t>Not recommend to use this bank. Trying to cheat with customers!</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Ainars-st</t>
+          <t>Dennyuu</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>2025-09-26T08:13:49-07:00</t>
+          <t>2025-05-19T06:23:28-07:00</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>13187722367</t>
+          <t>12673561062</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id302645165</t>
+          <t>https://itunes.apple.com/lv/reviews/id634056739</t>
         </is>
       </c>
       <c r="K77" s="2" t="n">
@@ -4577,21 +4577,21 @@
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Bad service</t>
+          <t>Отличная аппликация</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Not recommend to use this bank. Trying to cheat with customers!</t>
+          <t>Всё нравится</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Dennyuu</t>
+          <t>Инара123</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -4601,17 +4601,17 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>2025-05-19T06:23:28-07:00</t>
+          <t>2025-05-15T12:29:11-07:00</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>12673561062</t>
+          <t>12659844420</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id634056739</t>
+          <t>https://itunes.apple.com/lv/reviews/id1197238699</t>
         </is>
       </c>
       <c r="K78" s="2" t="n">
@@ -4630,41 +4630,41 @@
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Отличная аппликация</t>
+          <t>3D secure</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Всё нравится</t>
+          <t>Don't display pop ap or never processing after confirm</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Инара123</t>
+          <t>yavoitkun</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>2025-05-15T12:29:11-07:00</t>
+          <t>2025-04-25T03:28:44-07:00</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>12659844420</t>
+          <t>12583785194</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1197238699</t>
+          <t>https://itunes.apple.com/lv/reviews/id245236028</t>
         </is>
       </c>
       <c r="K79" s="2" t="n">
@@ -4687,17 +4687,17 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>3D secure</t>
+          <t>Mobile Scan</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>Don't display pop ap or never processing after confirm</t>
+          <t>Mobile scan isn't working as it did before. Now, when you need to enter your login number again and reach the section where you must input five digits, the mobile scan app doesn't let you in, displaying an incorrect PIN message. Only after refreshing the section does it approve your PIN. Poor service overall, and there is also no customer support available before 8:00 to provide direct assistance.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>yavoitkun</t>
+          <t>Pāvils K</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -4707,17 +4707,17 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>2025-04-25T03:28:44-07:00</t>
+          <t>2025-04-06T21:35:05-07:00</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>12583785194</t>
+          <t>12513395456</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id245236028</t>
+          <t>https://itunes.apple.com/lv/reviews/id1625623163</t>
         </is>
       </c>
       <c r="K80" s="2" t="n">
@@ -4740,37 +4740,37 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Mobile Scan</t>
+          <t>Jaunākā versija ļoti neērta</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Mobile scan isn't working as it did before. Now, when you need to enter your login number again and reach the section where you must input five digits, the mobile scan app doesn't let you in, displaying an incorrect PIN message. Only after refreshing the section does it approve your PIN. Poor service overall, and there is also no customer support available before 8:00 to provide direct assistance.</t>
+          <t>Pēc pēdējā apdeita no ļoti patīkami intuitīvas, informatīvas un loģiski izkārtotas, aplikācija ir pārvērtusies par instagramu - liela, nekādu funkciju nepildoša bilde pa pusi ekrāna un visas noderīgās lietas sastumtas dziļi apakšlīmeņos. booo</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Pāvils K</t>
+          <t>mjhdhcdrgv</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>2025-04-06T21:35:05-07:00</t>
+          <t>2025-01-27T22:39:18-07:00</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>12513395456</t>
+          <t>12239895359</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1625623163</t>
+          <t>https://itunes.apple.com/lv/reviews/id424619615</t>
         </is>
       </c>
       <c r="K81" s="2" t="n">
@@ -4793,17 +4793,17 @@
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Jaunākā versija ļoti neērta</t>
+          <t>Don’t</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Pēc pēdējā apdeita no ļoti patīkami intuitīvas, informatīvas un loģiski izkārtotas, aplikācija ir pārvērtusies par instagramu - liela, nekādu funkciju nepildoša bilde pa pusi ekrāna un visas noderīgās lietas sastumtas dziļi apakšlīmeņos. booo</t>
+          <t>Dont upgrade. It is absolutely awful !!!</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>mjhdhcdrgv</t>
+          <t>ggggedxcv</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -4813,17 +4813,17 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>2025-01-27T22:39:18-07:00</t>
+          <t>2024-12-21T10:17:41-07:00</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>12239895359</t>
+          <t>12089687475</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id424619615</t>
+          <t>https://itunes.apple.com/lv/reviews/id484976580</t>
         </is>
       </c>
       <c r="K82" s="2" t="n">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Don’t</t>
+          <t>My impressions of new software Citadele online</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>Dont upgrade. It is absolutely awful !!!</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>ggggedxcv</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>44.2</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>2024-12-21T10:17:41-07:00</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>12089687475</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>https://itunes.apple.com/lv/reviews/id484976580</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Latvia</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>lv</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>My impressions of new software Citadele online</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="inlineStr">
         <is>
           <t>From banking systems and particularly online banking systems we, clients, do expect first of all stability, reliability and zero errors. I have been told (Dagnija Lacis from Unisys/Baltic Technology Group) that some North American banks are still using software, created with programming language “Cobold”. It was a long time ago, but operational system in ATM’s is still Windows XP, created in early 2000. So, conservative approach with most stable and familiar software is typical for serious banking. I was very satisfied with previous software version. And the second window with comments: open this and You’ll be surprised, seems a behaviour a little over fine red line of good banking behaviour. I do not expect some fun from my internet banking,  so I always skip that window unopened. And I don’t see any crucial improvements. 
         Yours,
                     Harry Jirgensons</t>
         </is>
       </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>harryjirgensons1</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-19T03:35:52-07:00</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>11967323448</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id899519474</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Bring the widget back 🥲</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>I like a new design, but I want to have the widget back (it disappeared after the update). I would also like to see the purchase statistics</t>
+        </is>
+      </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>harryjirgensons1</t>
+          <t>Hello world 228</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -4921,17 +4921,17 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>2024-11-19T03:35:52-07:00</t>
+          <t>2024-11-09T01:24:34-07:00</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>11967323448</t>
+          <t>11929502864</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id899519474</t>
+          <t>https://itunes.apple.com/lv/reviews/id333444832</t>
         </is>
       </c>
       <c r="K84" s="2" t="n">
@@ -4950,21 +4950,21 @@
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Bring the widget back 🥲</t>
+          <t>Old version better</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>I like a new design, but I want to have the widget back (it disappeared after the update). I would also like to see the purchase statistics</t>
+          <t>.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Hello world 228</t>
+          <t>Snezokllv</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -4974,17 +4974,17 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>2024-11-09T01:24:34-07:00</t>
+          <t>2024-11-03T00:38:29-07:00</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>11929502864</t>
+          <t>11906524124</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id333444832</t>
+          <t>https://itunes.apple.com/lv/reviews/id309860745</t>
         </is>
       </c>
       <c r="K85" s="2" t="n">
@@ -5003,21 +5003,21 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Old version better</t>
+          <t>New update</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>Ļoti slikti saprotama aplikācija. Nulle norādes/pamaciba, kur kas ir mainījies. 10min mekleju ka var stapr kontiem naudu parskaitīt. Lojalitātes punkti ari vairak nav redzami - tos vēl nēsmu atradis......</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Snezokllv</t>
+          <t>mamamamarks</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -5027,17 +5027,17 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>2024-11-03T00:38:29-07:00</t>
+          <t>2024-10-31T11:18:07-07:00</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>11906524124</t>
+          <t>11896721624</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id309860745</t>
+          <t>https://itunes.apple.com/lv/reviews/id197646309</t>
         </is>
       </c>
       <c r="K86" s="2" t="n">
@@ -5056,21 +5056,21 @@
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>New update</t>
+          <t>New version</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Ļoti slikti saprotama aplikācija. Nulle norādes/pamaciba, kur kas ir mainījies. 10min mekleju ka var stapr kontiem naudu parskaitīt. Lojalitātes punkti ari vairak nav redzami - tos vēl nēsmu atradis......</t>
+          <t>Very bad. Everything that was on one screen is now hidden. And a bunch of unnecessary information that can't be removed.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>mamamamarks</t>
+          <t>MaxFyo</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -5080,17 +5080,17 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>2024-10-31T11:18:07-07:00</t>
+          <t>2024-10-30T12:23:43-07:00</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>11896721624</t>
+          <t>11893147382</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id197646309</t>
+          <t>https://itunes.apple.com/lv/reviews/id686343029</t>
         </is>
       </c>
       <c r="K87" s="2" t="n">
@@ -5113,17 +5113,17 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>New version</t>
+          <t>Jaunā versija ir briesmīga</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>Very bad. Everything that was on one screen is now hidden. And a bunch of unnecessary information that can't be removed.</t>
+          <t>Pusi ekrānu aizņem reklāmas un neko vairs nevar atrast</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>MaxFyo</t>
+          <t>Moriartijs</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -5133,17 +5133,17 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>2024-10-30T12:23:43-07:00</t>
+          <t>2024-10-30T04:08:51-07:00</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>11893147382</t>
+          <t>11891563650</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id686343029</t>
+          <t>https://itunes.apple.com/lv/reviews/id303463227</t>
         </is>
       </c>
       <c r="K88" s="2" t="n">
@@ -5162,21 +5162,21 @@
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>Jaunā versija ir briesmīga</t>
+          <t>Jaunā versija</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>Pusi ekrānu aizņem reklāmas un neko vairs nevar atrast</t>
+          <t>Pēc atjauninājuma nerādās widget ātrais atlikums. Pati aplikācija patīk un ir ērti lietojama. Ios versija 18.0.1</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Moriartijs</t>
+          <t>VirusStyle</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -5186,17 +5186,17 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>2024-10-30T04:08:51-07:00</t>
+          <t>2024-10-29T10:05:35-07:00</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>11891563650</t>
+          <t>11888892762</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id303463227</t>
+          <t>https://itunes.apple.com/lv/reviews/id174655423</t>
         </is>
       </c>
       <c r="K89" s="2" t="n">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
@@ -5224,12 +5224,12 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>Pēc atjauninājuma nerādās widget ātrais atlikums. Pati aplikācija patīk un ir ērti lietojama. Ios versija 18.0.1</t>
+          <t>Jaunā versija ir kļuvusi sarežģītāka, mazāk patīkama. Vairāk laika un čakara pārslēgties no privātā uz biznesa kontu un apskatīt visus kontus. Tagad pārāk daudz mistiski piedāvājumi un reklàmas</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>VirusStyle</t>
+          <t>andriskaposts</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -5239,17 +5239,17 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>2024-10-29T10:05:35-07:00</t>
+          <t>2024-10-29T00:05:03-07:00</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>11888892762</t>
+          <t>11887150057</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id174655423</t>
+          <t>https://itunes.apple.com/lv/reviews/id1381525443</t>
         </is>
       </c>
       <c r="K90" s="2" t="n">
@@ -5268,21 +5268,22 @@
         </is>
       </c>
       <c r="C91" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Jaunā versija</t>
+          <t>Наконец то!</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>Jaunā versija ir kļuvusi sarežģītāka, mazāk patīkama. Vairāk laika un čakara pārslēgties no privātā uz biznesa kontu un apskatīt visus kontus. Tagad pārāk daudz mistiski piedāvājumi un reklàmas</t>
+          <t>Пользовался SEB еще неделю назад, все говорили что вы ахуенные. Не верил, потому что в Латвии такого быть не может. Все через одно место.  
+приятно удивлен! Эффект ВАУ получил от пользования вашего приложения. машины!!! Так держать 🫡🚀</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>andriskaposts</t>
+          <t>Terek89</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -5292,17 +5293,17 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>2024-10-29T00:05:03-07:00</t>
+          <t>2024-10-27T01:56:02-07:00</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>11887150057</t>
+          <t>11880100160</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1381525443</t>
+          <t>https://itunes.apple.com/lv/reviews/id200358567</t>
         </is>
       </c>
       <c r="K91" s="2" t="n">
@@ -5321,22 +5322,21 @@
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Наконец то!</t>
+          <t>Widgets</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>Пользовался SEB еще неделю назад, все говорили что вы ахуенные. Не верил, потому что в Латвии такого быть не может. Все через одно место.  
-приятно удивлен! Эффект ВАУ получил от пользования вашего приложения. машины!!! Так держать 🫡🚀</t>
+          <t>Pēc atjauninājuma pazuda widzets 😔</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Terek89</t>
+          <t>Mar1sZ</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -5346,17 +5346,17 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>2024-10-27T01:56:02-07:00</t>
+          <t>2024-10-26T08:42:52-07:00</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>11880100160</t>
+          <t>11877476720</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id200358567</t>
+          <t>https://itunes.apple.com/lv/reviews/id493922254</t>
         </is>
       </c>
       <c r="K92" s="2" t="n">
@@ -5375,21 +5375,21 @@
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Widgets</t>
+          <t>App update</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Pēc atjauninājuma pazuda widzets 😔</t>
+          <t>Galīgi garām- galvenajā lapā tagad zem galvenā konta ir reklāma!  Pirms tam bija redzami visi konti. Tagad papildus jāpiespiež VISI konti, lai redzētu, kas notiek pārējos. Atgrieziet, lūdzu , galveno skatu ar visiem kontiem!</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Mar1sZ</t>
+          <t>Zanete9</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -5399,17 +5399,17 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>2024-10-26T08:42:52-07:00</t>
+          <t>2024-10-25T09:32:22-07:00</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>11877476720</t>
+          <t>11873774178</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id493922254</t>
+          <t>https://itunes.apple.com/lv/reviews/id356476596</t>
         </is>
       </c>
       <c r="K93" s="2" t="n">
@@ -5428,21 +5428,21 @@
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>App update</t>
+          <t>Widget removed</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>Galīgi garām- galvenajā lapā tagad zem galvenā konta ir reklāma!  Pirms tam bija redzami visi konti. Tagad papildus jāpiespiež VISI konti, lai redzētu, kas notiek pārējos. Atgrieziet, lūdzu , galveno skatu ar visiem kontiem!</t>
+          <t>Hate that you have removed widget for quickly checking account balance.</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Zanete9</t>
+          <t>Sezo1!</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>2024-10-25T09:32:22-07:00</t>
+          <t>2024-10-24T04:45:23-07:00</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>11873774178</t>
+          <t>11869101241</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id356476596</t>
+          <t>https://itunes.apple.com/lv/reviews/id421156522</t>
         </is>
       </c>
       <c r="K94" s="2" t="n">
@@ -5485,72 +5485,72 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Widget removed</t>
+          <t>Revolut bez revolūcijas</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
-        <is>
-          <t>Hate that you have removed widget for quickly checking account balance.</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>Sezo1!</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>44.0</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>2024-10-24T04:45:23-07:00</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>11869101241</t>
-        </is>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>https://itunes.apple.com/lv/reviews/id421156522</t>
-        </is>
-      </c>
-      <c r="K95" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>Latvia</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>lv</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>Revolut bez revolūcijas</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
         <is>
           <t>Google Tag Manager, Facebook SDK ir ieslēgtas pēc noklusējuma. Atrodas īsti neatrodamā vietā. Jūs esat banka vai vietne ar receptēm?
 Ar ikonām, kuras pārdeva kaut kādabetting platforma. Neapmierina, ka uz lielā telefona neietilpst bez ritināšanas: mani konti, mani maksājumi un iestatījumi.
 Kopsavilkums: šī ir lietotne pusakliem, bezgaumīgiem spēlmaņiem. Skumji 😢</t>
         </is>
       </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>vershart</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-23T12:50:14-07:00</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>11866920387</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id533968658</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>New app look🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>Amazing job done by development and design team! 🔥 app looks outstanding! Big thanks!🫶🏻</t>
+        </is>
+      </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>vershart</t>
+          <t>Denchill21</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -5560,17 +5560,17 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>2024-10-23T12:50:14-07:00</t>
+          <t>2024-10-23T08:32:33-07:00</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>11866920387</t>
+          <t>11866172369</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id533968658</t>
+          <t>https://itunes.apple.com/lv/reviews/id1315685789</t>
         </is>
       </c>
       <c r="K96" s="2" t="n">
@@ -5589,41 +5589,41 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>New app look🔥🔥🔥</t>
+          <t>Poor user experience</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>Amazing job done by development and design team! 🔥 app looks outstanding! Big thanks!🫶🏻</t>
+          <t>Outdated design and limited functionality of the app. Unclear transaction history with delayed transactions being shown out of sequence. Only the date of transaction is specified, but not the time. 3D secure is much more inconvenient to use, compared to SmartID. Please explore the interface of Chase UK and consider making improvements to Citadele banking app.</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Denchill21</t>
+          <t>34 vsk</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>2024-10-23T08:32:33-07:00</t>
+          <t>2024-09-30T05:34:19-07:00</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>11866172369</t>
+          <t>11781257580</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1315685789</t>
+          <t>https://itunes.apple.com/lv/reviews/id297713306</t>
         </is>
       </c>
       <c r="K97" s="2" t="n">
@@ -5642,41 +5642,41 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Poor user experience</t>
+          <t>Citadele</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>Outdated design and limited functionality of the app. Unclear transaction history with delayed transactions being shown out of sequence. Only the date of transaction is specified, but not the time. 3D secure is much more inconvenient to use, compared to SmartID. Please explore the interface of Chase UK and consider making improvements to Citadele banking app.</t>
+          <t>Labākā banku aplikācija</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>34 vsk</t>
+          <t>Sakals</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>2024-09-30T05:34:19-07:00</t>
+          <t>2024-06-25T07:24:11-07:00</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>11781257580</t>
+          <t>11421615443</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id297713306</t>
+          <t>https://itunes.apple.com/lv/reviews/id42359889</t>
         </is>
       </c>
       <c r="K98" s="2" t="n">
@@ -5699,37 +5699,37 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Citadele</t>
+          <t>Citadel</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Labākā banku aplikācija</t>
+          <t>Iesaku! 🤩</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Sakals</t>
+          <t>azakin78</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>2024-06-25T07:24:11-07:00</t>
+          <t>2024-05-10T02:39:38-07:00</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>11421615443</t>
+          <t>11251572473</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id42359889</t>
+          <t>https://itunes.apple.com/lv/reviews/id797903164</t>
         </is>
       </c>
       <c r="K99" s="2" t="n">
@@ -5752,37 +5752,37 @@
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Citadel</t>
+          <t>Viss labi pārdomāts</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>Iesaku! 🤩</t>
+          <t>Ērta, pārskatāma, viegli saprotama un izmantojama aplikācija. Ļoti patīk.</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>azakin78</t>
+          <t>Laumelle</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>2024-05-10T02:39:38-07:00</t>
+          <t>2024-03-20T00:23:59-07:00</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>11251572473</t>
+          <t>11064372679</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id797903164</t>
+          <t>https://itunes.apple.com/lv/reviews/id907753487</t>
         </is>
       </c>
       <c r="K100" s="2" t="n">
@@ -5801,41 +5801,41 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Viss labi pārdomāts</t>
+          <t>Not version on iPad</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Ērta, pārskatāma, viegli saprotama un izmantojama aplikācija. Ļoti patīk.</t>
+          <t>I want version on iPad</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Laumelle</t>
+          <t>rek1ngs</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>2024-03-20T00:23:59-07:00</t>
+          <t>2024-03-05T10:31:05-07:00</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>11064372679</t>
+          <t>11011804833</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id907753487</t>
+          <t>https://itunes.apple.com/lv/reviews/id1409702477</t>
         </is>
       </c>
       <c r="K101" s="2" t="n">
@@ -5854,21 +5854,21 @@
         </is>
       </c>
       <c r="C102" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Not version on iPad</t>
+          <t>Love it</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>I want version on iPad</t>
+          <t>Palīdz parsutit naudu, sanemt naudu. iesaku visiem!</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>rek1ngs</t>
+          <t>𝐄𝐥𝐥𝐚𓆉</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -5878,17 +5878,17 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>2024-03-05T10:31:05-07:00</t>
+          <t>2024-03-04T07:16:56-07:00</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>11011804833</t>
+          <t>11007581975</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1409702477</t>
+          <t>https://itunes.apple.com/lv/reviews/id1234649714</t>
         </is>
       </c>
       <c r="K102" s="2" t="n">
@@ -5911,37 +5911,37 @@
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Love it</t>
+          <t>Best banking app ever</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Palīdz parsutit naudu, sanemt naudu. iesaku visiem!</t>
+          <t>I really like this app:)</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>𝐄𝐥𝐥𝐚𓆉</t>
+          <t>mlpplgip</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>2024-03-04T07:16:56-07:00</t>
+          <t>2024-02-24T08:45:02-07:00</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>11007581975</t>
+          <t>10975091972</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1234649714</t>
+          <t>https://itunes.apple.com/lv/reviews/id1482507137</t>
         </is>
       </c>
       <c r="K103" s="2" t="n">
@@ -5960,21 +5960,22 @@
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Best banking app ever</t>
+          <t>Quick balance not working</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>I really like this app:)</t>
+          <t>In last couple months, constant message showing “SSL error” on the widget. Very annoying.
+Last iOS and last app version.</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>mlpplgip</t>
+          <t>dkrasilnikov87</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -5984,17 +5985,17 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>2024-02-24T08:45:02-07:00</t>
+          <t>2024-02-22T21:28:50-07:00</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>10975091972</t>
+          <t>10969502166</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1482507137</t>
+          <t>https://itunes.apple.com/lv/reviews/id1285648071</t>
         </is>
       </c>
       <c r="K104" s="2" t="n">
@@ -6022,13 +6023,12 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>In last couple months, constant message showing “SSL error” on the widget. Very annoying.
-Last iOS and last app version.</t>
+          <t>Quick balance widget stopped working for last two months showing SSL error. Before that it was updating the balance only after the app itself was opened, which made it barely useful</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>dkrasilnikov87</t>
+          <t>zeco2309</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -6038,17 +6038,17 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>2024-02-22T21:28:50-07:00</t>
+          <t>2024-02-12T00:43:08-07:00</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>10969502166</t>
+          <t>10929966350</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1285648071</t>
+          <t>https://itunes.apple.com/lv/reviews/id101566404</t>
         </is>
       </c>
       <c r="K105" s="2" t="n">
@@ -6067,21 +6067,21 @@
         </is>
       </c>
       <c r="C106" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Quick balance not working</t>
+          <t>Ātrais atlikums lielākoties nestrādā</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>Quick balance widget stopped working for last two months showing SSL error. Before that it was updating the balance only after the app itself was opened, which made it barely useful</t>
+          <t>Jau vairāk kā mēnesi gaidu, kad tiks sakārtota opcija par ātro atlikumu un būs programmas atjauninājums. Šī problēma ir ļoti regulāra, priekš kam piedāvāt tādu opciju, ja vienmēr ir SSL error??? Vienmēr jāiet bankā, lai paskatītos atlikumu, taču nodrošiniet aplikācijas pilnveidīgu funkcionēšanu, šī ir bankas aplikācija nevis spēlītes… pati banka pilnīgi apmierina, bet mūžīgi ķibeles ar aplikāciju.</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>zeco2309</t>
+          <t>RozeeEl</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -6091,17 +6091,17 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>2024-02-12T00:43:08-07:00</t>
+          <t>2024-02-09T10:49:38-07:00</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>10929966350</t>
+          <t>10920582816</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id101566404</t>
+          <t>https://itunes.apple.com/lv/reviews/id832314400</t>
         </is>
       </c>
       <c r="K106" s="2" t="n">
@@ -6124,17 +6124,17 @@
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Ātrais atlikums lielākoties nestrādā</t>
+          <t>Widget is not working</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>Jau vairāk kā mēnesi gaidu, kad tiks sakārtota opcija par ātro atlikumu un būs programmas atjauninājums. Šī problēma ir ļoti regulāra, priekš kam piedāvāt tādu opciju, ja vienmēr ir SSL error??? Vienmēr jāiet bankā, lai paskatītos atlikumu, taču nodrošiniet aplikācijas pilnveidīgu funkcionēšanu, šī ir bankas aplikācija nevis spēlītes… pati banka pilnīgi apmierina, bet mūžīgi ķibeles ar aplikāciju.</t>
+          <t>Widget is not working on last ios version due to an SSL error</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>RozeeEl</t>
+          <t>Ricchi Ricch</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -6144,17 +6144,17 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>2024-02-09T10:49:38-07:00</t>
+          <t>2024-02-06T09:42:29-07:00</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>10920582816</t>
+          <t>10909249974</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id832314400</t>
+          <t>https://itunes.apple.com/lv/reviews/id406941781</t>
         </is>
       </c>
       <c r="K107" s="2" t="n">
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
@@ -6182,12 +6182,12 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>Widget is not working on last ios version due to an SSL error</t>
+          <t>I have instant SSL issue on the widget. Reinstall did not work.</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Ricchi Ricch</t>
+          <t>alastarfox</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -6197,17 +6197,17 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>2024-02-06T09:42:29-07:00</t>
+          <t>2024-02-05T04:36:45-07:00</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>10909249974</t>
+          <t>10904428818</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id406941781</t>
+          <t>https://itunes.apple.com/lv/reviews/id136066300</t>
         </is>
       </c>
       <c r="K108" s="2" t="n">
@@ -6226,76 +6226,76 @@
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Widget is not working</t>
+          <t>Widget error</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>I have instant SSL issue on the widget. Reinstall did not work.</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>alastarfox</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>13.7</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>2024-02-05T04:36:45-07:00</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>10904428818</t>
-        </is>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>https://itunes.apple.com/lv/reviews/id136066300</t>
-        </is>
-      </c>
-      <c r="K109" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>Latvia</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>lv</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>Widget error</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
         <is>
           <t>The most useful funtion not working anymore.
 Latest iOS/device and Citadele app. 
 2 stars for good app with push notification. 3 more stars will be when widgets will work again</t>
         </is>
       </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>walkerS07</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-03T03:09:21-07:00</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>10896344614</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id141053556</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>Face id does not work</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>I'm constantly getting an error message when I'm trying to activate the Face Id</t>
+        </is>
+      </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>walkerS07</t>
+          <t>mortex231094</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -6305,17 +6305,17 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>2024-02-03T03:09:21-07:00</t>
+          <t>2024-02-01T15:11:21-07:00</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>10896344614</t>
+          <t>10890452120</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id141053556</t>
+          <t>https://itunes.apple.com/lv/reviews/id553444918</t>
         </is>
       </c>
       <c r="K110" s="2" t="n">
@@ -6334,21 +6334,21 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Face id does not work</t>
+          <t>widget error</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>I'm constantly getting an error message when I'm trying to activate the Face Id</t>
+          <t>Newest ios version but still doesn’t work widget, “SSL error” almost few months</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>mortex231094</t>
+          <t>bublik02</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -6358,17 +6358,17 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>2024-02-01T15:11:21-07:00</t>
+          <t>2024-02-01T00:58:33-07:00</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>10890452120</t>
+          <t>10887912242</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id553444918</t>
+          <t>https://itunes.apple.com/lv/reviews/id651196055</t>
         </is>
       </c>
       <c r="K111" s="2" t="n">
@@ -6387,41 +6387,41 @@
         </is>
       </c>
       <c r="C112" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>widget error</t>
+          <t>App crash</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>Newest ios version but still doesn’t work widget, “SSL error” almost few months</t>
+          <t>„An SSL error has occured and a secure connection to the server cannot be made on iOS 14.8” Week ago everything worked fine</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>bublik02</t>
+          <t>usdvgh</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>12.48</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>2024-02-01T00:58:33-07:00</t>
+          <t>2024-01-12T22:41:55-07:00</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>10887912242</t>
+          <t>10816064645</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id651196055</t>
+          <t>https://itunes.apple.com/lv/reviews/id1567530686</t>
         </is>
       </c>
       <c r="K112" s="2" t="n">
@@ -6440,41 +6440,42 @@
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>App crash</t>
+          <t>Netieku aplikācijā!</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>„An SSL error has occured and a secure connection to the server cannot be made on iOS 14.8” Week ago everything worked fine</t>
+          <t>ejot aplikācijā un spiežot pieslēgties izmet kļūdu ka ir problēma ar SSL, nevar droši pieslēgties. Visu dienu mēģinu jau tikt aplikācijā!! 
+Iepriekš problēmu nebija.</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>usdvgh</t>
+          <t>Nickwitha</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>12.48</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>2024-01-12T22:41:55-07:00</t>
+          <t>2023-12-19T03:34:48-07:00</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>10816064645</t>
+          <t>10716910882</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1567530686</t>
+          <t>https://itunes.apple.com/lv/reviews/id1349178942</t>
         </is>
       </c>
       <c r="K113" s="2" t="n">
@@ -6493,42 +6494,41 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Netieku aplikācijā!</t>
+          <t>Tranzakcijas problēmas</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>ejot aplikācijā un spiežot pieslēgties izmet kļūdu ka ir problēma ar SSL, nevar droši pieslēgties. Visu dienu mēģinu jau tikt aplikācijā!! 
-Iepriekš problēmu nebija.</t>
+          <t>Vienmēr kaut kadi tur darbi notiek  , tā nevar zibmaksājumu veikt , tā nevar Ienākt banka , vienmēr atradīsies kaut kāda problēma vai kļūda kura jums truces darboties , tāpēc laipni Lūgti Citadele un atsuksmes kur ir 5 star tas ir fake , lietoju jūsu banku tāpēc ka nav citas izvēles diemžēl  , paldies par labu servisu , aplikācija ir problemātikas katru reizi</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Nickwitha</t>
+          <t>Janis 0zols</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>2023-12-19T03:34:48-07:00</t>
+          <t>2023-12-09T03:36:35-07:00</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>10716910882</t>
+          <t>10673996577</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1349178942</t>
+          <t>https://itunes.apple.com/lv/reviews/id1527333568</t>
         </is>
       </c>
       <c r="K114" s="2" t="n">
@@ -6547,41 +6547,41 @@
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Tranzakcijas problēmas</t>
+          <t>Mobile scan nestrādā</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Vienmēr kaut kadi tur darbi notiek  , tā nevar zibmaksājumu veikt , tā nevar Ienākt banka , vienmēr atradīsies kaut kāda problēma vai kļūda kura jums truces darboties , tāpēc laipni Lūgti Citadele un atsuksmes kur ir 5 star tas ir fake , lietoju jūsu banku tāpēc ka nav citas izvēles diemžēl  , paldies par labu servisu , aplikācija ir problemātikas katru reizi</t>
+          <t>Nav iespējams nekādā veidā noskenēt kodu, ja tas ir telefona ekrānā. Mobile scan ir iespējams lietot tikai tad, ja maksājumi tiek veikti no datora. Ļoti neērti un bezjēdzīgi.</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Janis 0zols</t>
+          <t>SJ9811</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>2023-12-09T03:36:35-07:00</t>
+          <t>2023-09-12T02:15:50-07:00</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>10673996577</t>
+          <t>10360107536</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1527333568</t>
+          <t>https://itunes.apple.com/lv/reviews/id584257643</t>
         </is>
       </c>
       <c r="K115" s="2" t="n">
@@ -6600,21 +6600,21 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Mobile scan nestrādā</t>
+          <t>Ikonas</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>Nav iespējams nekādā veidā noskenēt kodu, ja tas ir telefona ekrānā. Mobile scan ir iespējams lietot tikai tad, ja maksājumi tiek veikti no datora. Ļoti neērti un bezjēdzīgi.</t>
+          <t>Man patīn kad ir jaunas lietotnes ikonas</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>SJ9811</t>
+          <t>🧷Ziko🧷</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -6624,17 +6624,17 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>2023-09-12T02:15:50-07:00</t>
+          <t>2023-09-02T22:04:48-07:00</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>10360107536</t>
+          <t>10328645033</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id584257643</t>
+          <t>https://itunes.apple.com/lv/reviews/id1350016099</t>
         </is>
       </c>
       <c r="K116" s="2" t="n">
@@ -6653,41 +6653,41 @@
         </is>
       </c>
       <c r="C117" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Ikonas</t>
+          <t>Ну косяк же</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>Man patīn kad ir jaunas lietotnes ikonas</t>
+          <t>Когда после введения логина-пароля аппликация спрашивает код и переключаюсь на фото кодовой карты и обратно - нет возможности этот код ввести, виртуальная клавиатура больше не доступна. Тап что аппликацию использовать совершенно не возможно.</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>🧷Ziko🧷</t>
+          <t>Alex-7375</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>2023-09-02T22:04:48-07:00</t>
+          <t>2023-05-24T02:21:43-07:00</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>10328645033</t>
+          <t>9959835797</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1350016099</t>
+          <t>https://itunes.apple.com/lv/reviews/id399118566</t>
         </is>
       </c>
       <c r="K117" s="2" t="n">
@@ -6706,21 +6706,21 @@
         </is>
       </c>
       <c r="C118" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Ну косяк же</t>
+          <t>SSL kļūda</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>Когда после введения логина-пароля аппликация спрашивает код и переключаюсь на фото кодовой карты и обратно - нет возможности этот код ввести, виртуальная клавиатура больше не доступна. Тап что аппликацию использовать совершенно не возможно.</t>
+          <t>Pirms atvērt aplikāciju raksta SSL kļūda…nezinu vai tas ietekmē drošību atvērot..bet nav patīkami to redzēt.</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Alex-7375</t>
+          <t>Lvdelfi</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -6730,17 +6730,17 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>2023-05-24T02:21:43-07:00</t>
+          <t>2023-05-05T09:39:38-07:00</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>9959835797</t>
+          <t>9895755133</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id399118566</t>
+          <t>https://itunes.apple.com/lv/reviews/id244766505</t>
         </is>
       </c>
       <c r="K118" s="2" t="n">
@@ -6759,41 +6759,41 @@
         </is>
       </c>
       <c r="C119" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>SSL kļūda</t>
+          <t>Melns ekrāns</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>Pirms atvērt aplikāciju raksta SSL kļūda…nezinu vai tas ietekmē drošību atvērot..bet nav patīkami to redzēt.</t>
+          <t>Ļoti bieži izmantojot MobileScan atver lietotni un ir melns ekrāns, tad atkal par jaunu un tikai tad aiziet. Bieži arī vienkārši atverot aplikāciju ir tieši šī pati problēma, melns ekrāns un viss. Man ir Iphone 13 Pro Max, jaunākā Ios versija, aplikācija arī Citadele atjaunināta. Nekas nelīdz. Un šis jau ir vairākus mēnešus. Ļoti apgrūtina veikt maksājumus internetā!</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Lvdelfi</t>
+          <t>Badddaa</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>2023-05-05T09:39:38-07:00</t>
+          <t>2023-04-01T13:34:09-07:00</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>9895755133</t>
+          <t>9776448917</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id244766505</t>
+          <t>https://itunes.apple.com/lv/reviews/id521495447</t>
         </is>
       </c>
       <c r="K119" s="2" t="n">
@@ -6812,21 +6812,21 @@
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Melns ekrāns</t>
+          <t>…овноприложение</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>Ļoti bieži izmantojot MobileScan atver lietotni un ir melns ekrāns, tad atkal par jaunu un tikai tad aiziet. Bieži arī vienkārši atverot aplikāciju ir tieši šī pati problēma, melns ekrāns un viss. Man ir Iphone 13 Pro Max, jaunākā Ios versija, aplikācija arī Citadele atjaunināta. Nekas nelīdz. Un šis jau ir vairākus mēnešus. Ļoti apgrūtina veikt maksājumus internetā!</t>
+          <t>После обновления , мобильное приложения перестало работать, при любой операции выдает ошибку,приложение снес с телефона, теперь не могу заинсталить заного, полный отстой</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Badddaa</t>
+          <t>Android444</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -6836,17 +6836,17 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>2023-04-01T13:34:09-07:00</t>
+          <t>2023-03-19T09:27:38-07:00</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>9776448917</t>
+          <t>9730504104</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id521495447</t>
+          <t>https://itunes.apple.com/lv/reviews/id1174712803</t>
         </is>
       </c>
       <c r="K120" s="2" t="n">
@@ -6869,17 +6869,17 @@
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>…овноприложение</t>
+          <t>Melns ekrāns</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>После обновления , мобильное приложения перестало работать, при любой операции выдает ошибку,приложение снес с телефона, теперь не могу заинсталить заного, полный отстой</t>
+          <t>Aplikācija uzkarās, un katru reizi tā jādzēš ārā un jāinstalē no jauna. Tad notiek jau aptuveni gada griezumā. Vidēji 2-3 reizes mēnesī.</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Android444</t>
+          <t>diaaaaassss</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -6889,17 +6889,17 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>2023-03-19T09:27:38-07:00</t>
+          <t>2023-03-14T05:09:08-07:00</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>9730504104</t>
+          <t>9712186505</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1174712803</t>
+          <t>https://itunes.apple.com/lv/reviews/id953526853</t>
         </is>
       </c>
       <c r="K121" s="2" t="n">
@@ -6927,32 +6927,32 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>Aplikācija uzkarās, un katru reizi tā jādzēš ārā un jāinstalē no jauna. Tad notiek jau aptuveni gada griezumā. Vidēji 2-3 reizes mēnesī.</t>
+          <t>Kārtējo reizi ir aplukācija jāpārinstalē, jo parādās melns ekrāns. Tas ir kaitinoši.</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>diaaaaassss</t>
+          <t>Best suricata</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>12.48</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>2023-03-14T05:09:08-07:00</t>
+          <t>2023-02-26T03:26:40-07:00</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>9712186505</t>
+          <t>9657260669</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id953526853</t>
+          <t>https://itunes.apple.com/lv/reviews/id326775101</t>
         </is>
       </c>
       <c r="K122" s="2" t="n">
@@ -6971,21 +6971,22 @@
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Melns ekrāns</t>
+          <t>Red scren bug</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Kārtējo reizi ir aplukācija jāpārinstalē, jo parādās melns ekrāns. Tas ir kaitinoši.</t>
+          <t>3 no 5 reizēm,kad mēģinu atvērt aplikāciju,parādās sarkans ekrāns un jāver vaļā pa jaunu. Gan vecajam,gan jaunajam telefonam.   Citiem paziņām ir tāda pati problēma. Tehniskais serviss ne visai pieklājīgi atbild,lai pārbaudu,vai man ir jaunākā versija. Bet pēc pārējām atsauksmēm ir skaidrs,ka daudziem ir šī problēma. 
+3x from 5 when opening app,there is just red screen. On old and new phone the same. Also other friends have the same bug. When writing to tehnical help,they are not very polite and just answers that i need to check if i have newest version. But from other reviews it's clear that many users have similar problems.</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Best suricata</t>
+          <t>evijavarta</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -6995,17 +6996,17 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>2023-02-26T03:26:40-07:00</t>
+          <t>2023-02-19T07:32:29-07:00</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>9657260669</t>
+          <t>9634102041</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id326775101</t>
+          <t>https://itunes.apple.com/lv/reviews/id596817186</t>
         </is>
       </c>
       <c r="K123" s="2" t="n">
@@ -7024,22 +7025,21 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Red scren bug</t>
+          <t>Mobila aplikacija nestrada</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>3 no 5 reizēm,kad mēģinu atvērt aplikāciju,parādās sarkans ekrāns un jāver vaļā pa jaunu. Gan vecajam,gan jaunajam telefonam.   Citiem paziņām ir tāda pati problēma. Tehniskais serviss ne visai pieklājīgi atbild,lai pārbaudu,vai man ir jaunākā versija. Bet pēc pārējām atsauksmēm ir skaidrs,ka daudziem ir šī problēma. 
-3x from 5 when opening app,there is just red screen. On old and new phone the same. Also other friends have the same bug. When writing to tehnical help,they are not very polite and just answers that i need to check if i have newest version. But from other reviews it's clear that many users have similar problems.</t>
+          <t>Reti, kad mobila aplikacija ir lietojama. Jau kadu menesi bija melns ekrans, tagad sarkans ekrans. Cik reizes jau neesmu izdzesusi aplikaciju, un atpakal instaleju. zel!!</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>evijavarta</t>
+          <t>ievarinalds</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -7049,17 +7049,17 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>2023-02-19T07:32:29-07:00</t>
+          <t>2023-02-14T00:05:40-07:00</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>9634102041</t>
+          <t>9616068166</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id596817186</t>
+          <t>https://itunes.apple.com/lv/reviews/id641470460</t>
         </is>
       </c>
       <c r="K124" s="2" t="n">
@@ -7078,41 +7078,41 @@
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Mobila aplikacija nestrada</t>
+          <t>Problems using MobileScan</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Reti, kad mobila aplikacija ir lietojama. Jau kadu menesi bija melns ekrans, tagad sarkans ekrans. Cik reizes jau neesmu izdzesusi aplikaciju, un atpakal instaleju. zel!!</t>
+          <t>When trying to authenticate a purchase on the phone, app won’t open or give a notification about MobileScan authorisation.</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>ievarinalds</t>
+          <t>temporaryec</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>12.48</t>
+          <t>12.47</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>2023-02-14T00:05:40-07:00</t>
+          <t>2022-12-12T21:01:59-07:00</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>9616068166</t>
+          <t>9390560788</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id641470460</t>
+          <t>https://itunes.apple.com/lv/reviews/id1467648957</t>
         </is>
       </c>
       <c r="K125" s="2" t="n">
@@ -7131,21 +7131,21 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Problems using MobileScan</t>
+          <t>Salabojiet bugs!!!</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>When trying to authenticate a purchase on the phone, app won’t open or give a notification about MobileScan authorisation.</t>
+          <t>Katru nedēļu jāinstalē app no jauna… atvērot app - melns vai sarkans ekrāns… palīdz tikai ja nodzēš un ielādē app no jauna.</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>temporaryec</t>
+          <t>Ingridadem</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -7155,17 +7155,17 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>2022-12-12T21:01:59-07:00</t>
+          <t>2022-12-09T07:54:34-07:00</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>9390560788</t>
+          <t>9377831093</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1467648957</t>
+          <t>https://itunes.apple.com/lv/reviews/id199565521</t>
         </is>
       </c>
       <c r="K126" s="2" t="n">
@@ -7188,63 +7188,10 @@
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Salabojiet bugs!!!</t>
+          <t>Nekas pilnvērtīgi nestrādā!</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
-        <is>
-          <t>Katru nedēļu jāinstalē app no jauna… atvērot app - melns vai sarkans ekrāns… palīdz tikai ja nodzēš un ielādē app no jauna.</t>
-        </is>
-      </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>Ingridadem</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>12.47</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>2022-12-09T07:54:34-07:00</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t>9377831093</t>
-        </is>
-      </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>https://itunes.apple.com/lv/reviews/id199565521</t>
-        </is>
-      </c>
-      <c r="K127" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>Latvia</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>lv</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D128" s="3" t="inlineStr">
-        <is>
-          <t>Nekas pilnvērtīgi nestrādā!</t>
-        </is>
-      </c>
-      <c r="E128" s="3" t="inlineStr">
         <is>
           <t>Ātrais atlikums-neiet
 Paziņojumi-nenāk
@@ -7253,9 +7200,62 @@
 Vienu reizi jau pārinstalēju.</t>
         </is>
       </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Burlakss</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>12.47</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>2022-12-05T04:24:37-07:00</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>9363184138</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id538415840</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>terrible app</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>worst ever. Never co es up to IOS updates. If you want to live “off-line”, definetely choose this. Works out exactly in 50% cases</t>
+        </is>
+      </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Burlakss</t>
+          <t>donna-078</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -7265,17 +7265,17 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>2022-12-05T04:24:37-07:00</t>
+          <t>2022-12-02T13:35:15-07:00</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>9363184138</t>
+          <t>9353707439</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id538415840</t>
+          <t>https://itunes.apple.com/lv/reviews/id930873476</t>
         </is>
       </c>
       <c r="K128" s="2" t="n">
@@ -7298,17 +7298,17 @@
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>terrible app</t>
+          <t>Darbības problēmas</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>worst ever. Never co es up to IOS updates. If you want to live “off-line”, definetely choose this. Works out exactly in 50% cases</t>
+          <t>Nekas nemainās. Regulāri nevar apstiprināt maksājumus, atveras sarkans ekrāns un viss. Gadiem ilgas problēmas.</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>donna-078</t>
+          <t>Roliits</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -7318,17 +7318,17 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>2022-12-02T13:35:15-07:00</t>
+          <t>2022-10-23T13:05:24-07:00</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>9353707439</t>
+          <t>9215050290</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id930873476</t>
+          <t>https://itunes.apple.com/lv/reviews/id320430517</t>
         </is>
       </c>
       <c r="K129" s="2" t="n">
@@ -7351,37 +7351,37 @@
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Darbības problēmas</t>
+          <t>Citadele</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>Nekas nemainās. Regulāri nevar apstiprināt maksājumus, atveras sarkans ekrāns un viss. Gadiem ilgas problēmas.</t>
+          <t>Neiesaku lietot šo banku mani neapmierināja</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Roliits</t>
+          <t>Den4ik20188</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>12.47</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>2022-10-23T13:05:24-07:00</t>
+          <t>2022-08-27T05:18:13-07:00</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>9215050290</t>
+          <t>9022708714</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id320430517</t>
+          <t>https://itunes.apple.com/lv/reviews/id704507383</t>
         </is>
       </c>
       <c r="K130" s="2" t="n">
@@ -7400,21 +7400,21 @@
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Citadele</t>
+          <t>Citadele pielikums</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>Neiesaku lietot šo banku mani neapmierināja</t>
+          <t>Nestrādā! Regulāri pazūd! 😡</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>Den4ik20188</t>
+          <t>Mmmmmmbvvvvvhhhhh</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -7424,17 +7424,17 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>2022-08-27T05:18:13-07:00</t>
+          <t>2022-08-25T10:51:50-07:00</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>9022708714</t>
+          <t>9016127981</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id704507383</t>
+          <t>https://itunes.apple.com/lv/reviews/id1441355744</t>
         </is>
       </c>
       <c r="K131" s="2" t="n">
@@ -7457,17 +7457,17 @@
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Citadele pielikums</t>
+          <t>Kļūdas</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>Nestrādā! Regulāri pazūd! 😡</t>
+          <t>Regulāri nestradā maksājumi,īpaši no Tele2 un Enefit rēķiniem pa tiešo nevar veikt apmaksu</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>Mmmmmmbvvvvvhhhhh</t>
+          <t>Janusex44</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -7477,17 +7477,17 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>2022-08-25T10:51:50-07:00</t>
+          <t>2022-07-08T21:36:14-07:00</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>9016127981</t>
+          <t>8855345987</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1441355744</t>
+          <t>https://itunes.apple.com/lv/reviews/id156306618</t>
         </is>
       </c>
       <c r="K132" s="2" t="n">
@@ -7506,41 +7506,41 @@
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Kļūdas</t>
+          <t>Login issues</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Regulāri nestradā maksājumi,īpaši no Tele2 un Enefit rēķiniem pa tiešo nevar veikt apmaksu</t>
+          <t>After the latest update crashes 1 per 3 attempts to login</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Janusex44</t>
+          <t>pinkfreudmd</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>12.45</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>2022-07-08T21:36:14-07:00</t>
+          <t>2022-06-08T03:25:54-07:00</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>8855345987</t>
+          <t>8753056750</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id156306618</t>
+          <t>https://itunes.apple.com/lv/reviews/id963385833</t>
         </is>
       </c>
       <c r="K133" s="2" t="n">
@@ -7559,21 +7559,21 @@
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Login issues</t>
+          <t>Blank screen</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>After the latest update crashes 1 per 3 attempts to login</t>
+          <t>When I open app only 1 from 5 times app works normal, in other time i see only blank screen. And I should delete and re-install app one more time.</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>pinkfreudmd</t>
+          <t>Olga_22052022</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -7583,17 +7583,17 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>2022-06-08T03:25:54-07:00</t>
+          <t>2022-05-22T01:12:47-07:00</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>8753056750</t>
+          <t>8696042765</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id963385833</t>
+          <t>https://itunes.apple.com/lv/reviews/id1410921302</t>
         </is>
       </c>
       <c r="K134" s="2" t="n">
@@ -7612,21 +7612,21 @@
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Blank screen</t>
+          <t>Nice app</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>When I open app only 1 from 5 times app works normal, in other time i see only blank screen. And I should delete and re-install app one more time.</t>
+          <t>Please fix issue that app sometimes quits after 1 second</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Olga_22052022</t>
+          <t>ЙAARD</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -7636,17 +7636,17 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>2022-05-22T01:12:47-07:00</t>
+          <t>2022-05-20T05:21:10-07:00</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>8696042765</t>
+          <t>8689679733</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1410921302</t>
+          <t>https://itunes.apple.com/lv/reviews/id147247978</t>
         </is>
       </c>
       <c r="K135" s="2" t="n">
@@ -7665,21 +7665,21 @@
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Nice app</t>
+          <t>The Widget</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>Please fix issue that app sometimes quits after 1 second</t>
+          <t>This is a great banking app, there is no doubt in that, but when I open the app through the widget, it sometimes doesn’t authorise.</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>ЙAARD</t>
+          <t>Lion_Lv</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -7689,17 +7689,17 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>2022-05-20T05:21:10-07:00</t>
+          <t>2022-05-08T07:02:11-07:00</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>8689679733</t>
+          <t>8650131507</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id147247978</t>
+          <t>https://itunes.apple.com/lv/reviews/id794679289</t>
         </is>
       </c>
       <c r="K136" s="2" t="n">
@@ -7718,21 +7718,21 @@
         </is>
       </c>
       <c r="C137" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>The Widget</t>
+          <t>Black screen</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>This is a great banking app, there is no doubt in that, but when I open the app through the widget, it sometimes doesn’t authorise.</t>
+          <t>While paying with face ID sometimes just opens balck screen and its imposible to continue.</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Lion_Lv</t>
+          <t>EndijsO</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -7742,17 +7742,17 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>2022-05-08T07:02:11-07:00</t>
+          <t>2022-05-06T21:21:01-07:00</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>8650131507</t>
+          <t>8645114542</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id794679289</t>
+          <t>https://itunes.apple.com/lv/reviews/id944347544</t>
         </is>
       </c>
       <c r="K137" s="2" t="n">
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
@@ -7780,12 +7780,12 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>While paying with face ID sometimes just opens balck screen and its imposible to continue.</t>
+          <t>It is a great App. Except one issue. Often when I try to open App I see just black screen. It is annoying.</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>EndijsO</t>
+          <t>OleksandrKo</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -7795,17 +7795,17 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>2022-05-06T21:21:01-07:00</t>
+          <t>2022-05-02T01:39:05-07:00</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>8645114542</t>
+          <t>8628613993</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id944347544</t>
+          <t>https://itunes.apple.com/lv/reviews/id1398622639</t>
         </is>
       </c>
       <c r="K138" s="2" t="n">
@@ -7824,21 +7824,21 @@
         </is>
       </c>
       <c r="C139" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Black screen</t>
+          <t>Bugged</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>It is a great App. Except one issue. Often when I try to open App I see just black screen. It is annoying.</t>
+          <t>Bugged. The app does nothing when second pin code is entered.  No way to login with MobileScan.</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>OleksandrKo</t>
+          <t>Galliec</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -7848,17 +7848,17 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>2022-05-02T01:39:05-07:00</t>
+          <t>2022-04-27T02:18:59-07:00</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>8628613993</t>
+          <t>8610893337</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1398622639</t>
+          <t>https://itunes.apple.com/lv/reviews/id340678224</t>
         </is>
       </c>
       <c r="K139" s="2" t="n">
@@ -7881,17 +7881,17 @@
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Bugged</t>
+          <t>Works very bad.</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>Bugged. The app does nothing when second pin code is entered.  No way to login with MobileScan.</t>
+          <t>In comparison with orher banking apps this one is so so behind in development. A new card was delivered, I went to activate it and now it’s not displayed at all. I have to go to support for help? Also never shows fast balance.</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Galliec</t>
+          <t>nowaaay333</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -7901,17 +7901,17 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>2022-04-27T02:18:59-07:00</t>
+          <t>2022-04-26T14:38:39-07:00</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>8610893337</t>
+          <t>8609414521</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id340678224</t>
+          <t>https://itunes.apple.com/lv/reviews/id289628282</t>
         </is>
       </c>
       <c r="K140" s="2" t="n">
@@ -7930,41 +7930,41 @@
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Works very bad.</t>
+          <t>Иногда вылетает</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>In comparison with orher banking apps this one is so so behind in development. A new card was delivered, I went to activate it and now it’s not displayed at all. I have to go to support for help? Also never shows fast balance.</t>
+          <t>Иногда при входе в приложение появляется ошибка, из-за чего приложение вылетает. В остальном же приложение очень даже хорошо сделано</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>nowaaay333</t>
+          <t>Horowary</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>12.45</t>
+          <t>12.44</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>2022-04-26T14:38:39-07:00</t>
+          <t>2022-03-21T10:33:51-07:00</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>8609414521</t>
+          <t>8480509212</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id289628282</t>
+          <t>https://itunes.apple.com/lv/reviews/id1390982561</t>
         </is>
       </c>
       <c r="K141" s="2" t="n">
@@ -7983,21 +7983,22 @@
         </is>
       </c>
       <c r="C142" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Иногда вылетает</t>
+          <t>Par daudz kļūdu</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>Иногда при входе в приложение появляется ошибка, из-за чего приложение вылетает. В остальном же приложение очень даже хорошо сделано</t>
+          <t>Pirms update nebija problēmu, viss apmierināja. 
+Pēc update mani met ārā no aplikācijas, kad vēlos veikt maksājumu. Pin kodu jāievada 3x lai aplikacija saprastu ka tas ir īstais, jo visu laiku met kļūdu. Nu nevar bankai būt tāda aplikācija. Tai jābūt uzticamai, bet šobrīd tā tieši izskatās pēc krāpnieku versijas ar ļoti daudz aizdomīgiem gļukiem.</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Horowary</t>
+          <t>Anunamatata</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -8007,17 +8008,17 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>2022-03-21T10:33:51-07:00</t>
+          <t>2022-03-17T23:59:23-07:00</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>8480509212</t>
+          <t>8467745651</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1390982561</t>
+          <t>https://itunes.apple.com/lv/reviews/id1075324188</t>
         </is>
       </c>
       <c r="K142" s="2" t="n">
@@ -8040,18 +8041,17 @@
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Par daudz kļūdu</t>
+          <t>TouchID</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Pirms update nebija problēmu, viss apmierināja. 
-Pēc update mani met ārā no aplikācijas, kad vēlos veikt maksājumu. Pin kodu jāievada 3x lai aplikacija saprastu ka tas ir īstais, jo visu laiku met kļūdu. Nu nevar bankai būt tāda aplikācija. Tai jābūt uzticamai, bet šobrīd tā tieši izskatās pēc krāpnieku versijas ar ļoti daudz aizdomīgiem gļukiem.</t>
+          <t>Почему больше нельзя войти в свой счет через TouchID. Требует постоянно логин и пароль входа. Раньше все работало.</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>Anunamatata</t>
+          <t>ваадька</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -8061,17 +8061,17 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>2022-03-17T23:59:23-07:00</t>
+          <t>2022-03-03T02:58:23-07:00</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>8467745651</t>
+          <t>8415391591</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1075324188</t>
+          <t>https://itunes.apple.com/lv/reviews/id1066182224</t>
         </is>
       </c>
       <c r="K143" s="2" t="n">
@@ -8090,21 +8090,21 @@
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>TouchID</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>Почему больше нельзя войти в свой счет через TouchID. Требует постоянно логин и пароль входа. Раньше все работало.</t>
+          <t>Can’t get in my bank.</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>ваадька</t>
+          <t>Nohlahgus</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -8114,17 +8114,17 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>2022-03-03T02:58:23-07:00</t>
+          <t>2022-02-26T07:41:07-07:00</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>8415391591</t>
+          <t>8398694228</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1066182224</t>
+          <t>https://itunes.apple.com/lv/reviews/id917242110</t>
         </is>
       </c>
       <c r="K144" s="2" t="n">
@@ -8143,21 +8143,21 @@
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Пинкод</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Can’t get in my bank.</t>
+          <t>Не дает создать пинкод- пишет ошибку после повторения кода.</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Nohlahgus</t>
+          <t>Andrey Frost</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -8167,17 +8167,17 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>2022-02-26T07:41:07-07:00</t>
+          <t>2022-02-21T00:00:42-07:00</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>8398694228</t>
+          <t>8379726719</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id917242110</t>
+          <t>https://itunes.apple.com/lv/reviews/id586534715</t>
         </is>
       </c>
       <c r="K145" s="2" t="n">
@@ -8196,21 +8196,21 @@
         </is>
       </c>
       <c r="C146" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Пинкод</t>
+          <t>🥸</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>Не дает создать пинкод- пишет ошибку после повторения кода.</t>
+          <t>Face ID isn’t working and mobile scan isn’t working as well🥲</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>Andrey Frost</t>
+          <t>imvsmodel</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -8220,17 +8220,17 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>2022-02-21T00:00:42-07:00</t>
+          <t>2022-02-20T14:57:32-07:00</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>8379726719</t>
+          <t>8378503862</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id586534715</t>
+          <t>https://itunes.apple.com/lv/reviews/id1242888200</t>
         </is>
       </c>
       <c r="K146" s="2" t="n">
@@ -8253,17 +8253,17 @@
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>🥸</t>
+          <t>Logo</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Face ID isn’t working and mobile scan isn’t working as well🥲</t>
+          <t>New logo is terribly ugly.. return the previous one please</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>imvsmodel</t>
+          <t>jsjbtvjdjb</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -8273,17 +8273,17 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>2022-02-20T14:57:32-07:00</t>
+          <t>2022-02-19T01:54:18-07:00</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>8378503862</t>
+          <t>8372340601</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1242888200</t>
+          <t>https://itunes.apple.com/lv/reviews/id760296555</t>
         </is>
       </c>
       <c r="K147" s="2" t="n">
@@ -8302,41 +8302,41 @@
         </is>
       </c>
       <c r="C148" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Logo</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>New logo is terribly ugly.. return the previous one please</t>
+          <t>Hi. Since last update the app constantly asks for auth information like username. The checkbox "Saglabāt" ain't working.</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>jsjbtvjdjb</t>
+          <t>Sergejs.St</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>2022-02-19T01:54:18-07:00</t>
+          <t>2021-12-21T03:33:35-07:00</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>8372340601</t>
+          <t>8153201776</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id760296555</t>
+          <t>https://itunes.apple.com/lv/reviews/id1215224596</t>
         </is>
       </c>
       <c r="K148" s="2" t="n">
@@ -8355,21 +8355,21 @@
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Regulāri nobrūk aplikācija un Mobile scan.</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>Hi. Since last update the app constantly asks for auth information like username. The checkbox "Saglabāt" ain't working.</t>
+          <t>Miskaste ne aplikācija! Regulāri nobrūk Mobile scan, karās maksājumu saite uz aplikācijas apstiprināšanu. Ļoti slikts klientu serviss.</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>Sergejs.St</t>
+          <t>Jeekabsons</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -8379,17 +8379,17 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>2021-12-21T03:33:35-07:00</t>
+          <t>2021-12-05T01:03:42-07:00</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>8153201776</t>
+          <t>8097068557</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1215224596</t>
+          <t>https://itunes.apple.com/lv/reviews/id391428258</t>
         </is>
       </c>
       <c r="K149" s="2" t="n">
@@ -8408,21 +8408,21 @@
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Regulāri nobrūk aplikācija un Mobile scan.</t>
+          <t>Kļūda novērsta</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>Miskaste ne aplikācija! Regulāri nobrūk Mobile scan, karās maksājumu saite uz aplikācijas apstiprināšanu. Ļoti slikts klientu serviss.</t>
+          <t>Beidzot aplikācija strādā, tikai nepieciešams nevis apdeitot aplikāciju, bet gan izdzēst un tad reģistrēties. Tikai apdeitojot aplikāciju nav iespējams reģistrēties, joprojām parādās kļūdas paziņojums.</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>Jeekabsons</t>
+          <t>White House ghost</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -8432,17 +8432,17 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>2021-12-05T01:03:42-07:00</t>
+          <t>2021-12-03T02:45:09-07:00</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>8097068557</t>
+          <t>8089879447</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id391428258</t>
+          <t>https://itunes.apple.com/lv/reviews/id276215849</t>
         </is>
       </c>
       <c r="K150" s="2" t="n">
@@ -8461,41 +8461,41 @@
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>Kļūda novērsta</t>
+          <t>Kļūda</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Beidzot aplikācija strādā, tikai nepieciešams nevis apdeitot aplikāciju, bet gan izdzēst un tad reģistrēties. Tikai apdeitojot aplikāciju nav iespējams reģistrēties, joprojām parādās kļūdas paziņojums.</t>
+          <t>Uz iphone 13 ios 15.1 nevar izveidot paroli, izmetās kļūda.</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>White House ghost</t>
+          <t>Maucenaiks</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>2021-12-03T02:45:09-07:00</t>
+          <t>2021-10-28T10:04:31-07:00</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>8089879447</t>
+          <t>7963332877</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id276215849</t>
+          <t>https://itunes.apple.com/lv/reviews/id86935130</t>
         </is>
       </c>
       <c r="K151" s="2" t="n">
@@ -8514,21 +8514,21 @@
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Kļūda</t>
+          <t>Сплошное расстройство</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>Uz iphone 13 ios 15.1 nevar izveidot paroli, izmetās kļūda.</t>
+          <t>MobileScan в двадцать восемнадцатый раз «забывает» меня и вынуждает переться в банк, чтобы восстановить доступ к счетам с нужными лимитами. Редкостный говноexperience. Никакие чудо-кредитки, херо карты, и х реворды не спасают. Ухожу из банка.</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Maucenaiks</t>
+          <t>Mihails.Galuska</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -8538,17 +8538,17 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>2021-10-28T10:04:31-07:00</t>
+          <t>2021-10-19T12:32:20-07:00</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>7963332877</t>
+          <t>7932287047</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id86935130</t>
+          <t>https://itunes.apple.com/lv/reviews/id108465413</t>
         </is>
       </c>
       <c r="K152" s="2" t="n">
@@ -8571,17 +8571,17 @@
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Сплошное расстройство</t>
+          <t>Aplikācija neatbild, nekādas reakcijas no tehniskā atbalsta.</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>MobileScan в двадцать восемнадцатый раз «забывает» меня и вынуждает переться в банк, чтобы восстановить доступ к счетам с нужными лимитами. Редкостный говноexperience. Никакие чудо-кредитки, херо карты, и х реворды не спасают. Ухожу из банка.</t>
+          <t>Jaunākā aplikācijas versija ar iOS 14.7.1 nestrādā. Rāda nepareizu paroli. Izdodas ielogoties tikai pēc paroles maiņas. Nākošo reizi atkal rāda nepareizu paroli. Atbalsts ieteica pārinstalēt aplikāciju (taot nestrādā). Tālāku atbalstu neviens nesniedz. Es nespēju tikt pie saviem līdzekļiem un banka IGNORĒ un pat netaisās neko darīt?</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Mihails.Galuska</t>
+          <t>katyyy1111</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -8591,17 +8591,17 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>2021-10-19T12:32:20-07:00</t>
+          <t>2021-10-17T09:14:36-07:00</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>7932287047</t>
+          <t>7925130489</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id108465413</t>
+          <t>https://itunes.apple.com/lv/reviews/id1339911016</t>
         </is>
       </c>
       <c r="K153" s="2" t="n">
@@ -8620,41 +8620,41 @@
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Aplikācija neatbild, nekādas reakcijas no tehniskā atbalsta.</t>
+          <t>FaceID is not working anymore</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>Jaunākā aplikācijas versija ar iOS 14.7.1 nestrādā. Rāda nepareizu paroli. Izdodas ielogoties tikai pēc paroles maiņas. Nākošo reizi atkal rāda nepareizu paroli. Atbalsts ieteica pārinstalēt aplikāciju (taot nestrādā). Tālāku atbalstu neviens nesniedz. Es nespēju tikt pie saviem līdzekļiem un banka IGNORĒ un pat netaisās neko darīt?</t>
+          <t>Needed option is enabled. Tried to toggle few times, but no luck</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>katyyy1111</t>
+          <t>anton.wise</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>12.35</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>2021-10-17T09:14:36-07:00</t>
+          <t>2021-02-28T21:54:40-07:00</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>7925130489</t>
+          <t>7051530499</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id1339911016</t>
+          <t>https://itunes.apple.com/lv/reviews/id942397956</t>
         </is>
       </c>
       <c r="K154" s="2" t="n">
@@ -8673,41 +8673,41 @@
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>FaceID is not working anymore</t>
+          <t>Planšete</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Needed option is enabled. Tried to toggle few times, but no luck</t>
+          <t>Vai aplikācija nav piemērota planšetei? IPad pro11 2020. Uz ekrāna redzu telefona izmēra aplikāciju!</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>anton.wise</t>
+          <t>andaugs</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>12.33</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>2021-02-28T21:54:40-07:00</t>
+          <t>2021-01-29T20:47:28-07:00</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>7051530499</t>
+          <t>6930832392</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id942397956</t>
+          <t>https://itunes.apple.com/lv/reviews/id521904688</t>
         </is>
       </c>
       <c r="K155" s="2" t="n">
@@ -8730,37 +8730,37 @@
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Planšete</t>
+          <t>Notifikācijas nedarbojas</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>Vai aplikācija nav piemērota planšetei? IPad pro11 2020. Uz ekrāna redzu telefona izmēra aplikāciju!</t>
+          <t>Lietotne laba, bet ielikšu 5 zvaigznes kad beidzot salabosiet notifikācijas.</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>andaugs</t>
+          <t>Edgars Briedis</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>12.33</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>2021-01-29T20:47:28-07:00</t>
+          <t>2020-11-08T10:37:58-07:00</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>6930832392</t>
+          <t>6623313202</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id521904688</t>
+          <t>https://itunes.apple.com/lv/reviews/id159159681</t>
         </is>
       </c>
       <c r="K156" s="2" t="n">
@@ -8779,41 +8779,41 @@
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Notifikācijas nedarbojas</t>
+          <t>iOS 14</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Lietotne laba, bet ielikšu 5 zvaigznes kad beidzot salabosiet notifikācijas.</t>
+          <t>Pēc iOS 14 uzstādīšanas pazudis ātrais atlikums</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>Edgars Briedis</t>
+          <t>Dednikos</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>12.30</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>2020-11-08T10:37:58-07:00</t>
+          <t>2020-09-18T08:42:58-07:00</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>6623313202</t>
+          <t>6442181792</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id159159681</t>
+          <t>https://itunes.apple.com/lv/reviews/id643898752</t>
         </is>
       </c>
       <c r="K157" s="2" t="n">
@@ -8832,41 +8832,42 @@
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>iOS 14</t>
+          <t>No Notifications</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>Pēc iOS 14 uzstādīšanas pazudis ātrais atlikums</t>
+          <t>Push notifications for mobile scan, outgoing and incoming payments are no longer working. I even tried turning everything off and on again, but still no notifications.
+Edit: Reinstalling the app fixed the issue, however this should not have happenned. Keep better track of your user's data!</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>Dednikos</t>
+          <t>eggnukes</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>12.30</t>
+          <t>12.29</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>2020-09-18T08:42:58-07:00</t>
+          <t>2020-08-01T00:04:33-07:00</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>6442181792</t>
+          <t>6266226297</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id643898752</t>
+          <t>https://itunes.apple.com/lv/reviews/id593787385</t>
         </is>
       </c>
       <c r="K158" s="2" t="n">
@@ -8889,38 +8890,37 @@
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>No Notifications</t>
+          <t>Constant crashes</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>Push notifications for mobile scan, outgoing and incoming payments are no longer working. I even tried turning everything off and on again, but still no notifications.
-Edit: Reinstalling the app fixed the issue, however this should not have happenned. Keep better track of your user's data!</t>
+          <t>Updated to the latest version. Now my banking experience is close to something that happened during pre-Internet era. Everything is slow and constantly crashes.</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>eggnukes</t>
+          <t>Jurriss</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>12.29</t>
+          <t>12.27</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>2020-08-01T00:04:33-07:00</t>
+          <t>2020-07-21T10:28:18-07:00</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>6266226297</t>
+          <t>6224821081</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id593787385</t>
+          <t>https://itunes.apple.com/lv/reviews/id508109784</t>
         </is>
       </c>
       <c r="K159" s="2" t="n">
@@ -8943,17 +8943,17 @@
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Constant crashes</t>
+          <t>Atlikums</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>Updated to the latest version. Now my banking experience is close to something that happened during pre-Internet era. Everything is slow and constantly crashes.</t>
+          <t>Šķiet, ka pēc pēdējā app Update vairs nestrādā ātrā atlikuma opcija. iPhone 7 plus. OS pēdējā versija</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>Jurriss</t>
+          <t>uldka</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -8963,17 +8963,17 @@
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>2020-07-21T10:28:18-07:00</t>
+          <t>2020-07-14T03:58:48-07:00</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>6224821081</t>
+          <t>6196380957</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id508109784</t>
+          <t>https://itunes.apple.com/lv/reviews/id631406582</t>
         </is>
       </c>
       <c r="K160" s="2" t="n">
@@ -8992,41 +8992,41 @@
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Atlikums</t>
+          <t>Nepienāk SMS</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Šķiet, ka pēc pēdējā app Update vairs nestrādā ātrā atlikuma opcija. iPhone 7 plus. OS pēdējā versija</t>
+          <t>Vairs nepienāk SMS priekš mobilscan, pie iestatījumiem arī nav funkcijas lai atļautu SMS saņemšanu. iPhone xr</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>uldka</t>
+          <t>jrobb85</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>12.27</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>2020-07-14T03:58:48-07:00</t>
+          <t>2020-03-28T07:13:00-07:00</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>6196380957</t>
+          <t>5726249171</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id631406582</t>
+          <t>https://itunes.apple.com/lv/reviews/id450871962</t>
         </is>
       </c>
       <c r="K161" s="2" t="n">
@@ -9045,21 +9045,21 @@
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Nepienāk SMS</t>
+          <t>Top-1 in LV</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>Vairs nepienāk SMS priekš mobilscan, pie iestatījumiem arī nav funkcijas lai atļautu SMS saņemšanu. iPhone xr</t>
+          <t>Used banking apps in numerous countries - by far one of the best banking apps and top-1 in Latvia</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>jrobb85</t>
+          <t>RichaStick</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -9069,17 +9069,17 @@
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>2020-03-28T07:13:00-07:00</t>
+          <t>2020-03-22T01:19:42-07:00</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>5726249171</t>
+          <t>5695509155</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id450871962</t>
+          <t>https://itunes.apple.com/lv/reviews/id632218428</t>
         </is>
       </c>
       <c r="K162" s="2" t="n">
@@ -9102,17 +9102,17 @@
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>Top-1 in LV</t>
+          <t>Не открыть счёт с приложения</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>Used banking apps in numerous countries - by far one of the best banking apps and top-1 in Latvia</t>
+          <t>Открытие счёта в банке с помощью приложения вообще не работает. Зачем нужна функция, которая не допилена, во всяком случае на iphone?</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>RichaStick</t>
+          <t>Edimaks</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -9122,17 +9122,17 @@
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>2020-03-22T01:19:42-07:00</t>
+          <t>2020-03-19T11:06:32-07:00</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>5695509155</t>
+          <t>5683196586</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id632218428</t>
+          <t>https://itunes.apple.com/lv/reviews/id275598331</t>
         </is>
       </c>
       <c r="K163" s="2" t="n">
@@ -9155,17 +9155,17 @@
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Не открыть счёт с приложения</t>
+          <t>9/10</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>Открытие счёта в банке с помощью приложения вообще не работает. Зачем нужна функция, которая не допилена, во всяком случае на iphone?</t>
+          <t>Очень крутой банк. Было бы идеально, если можно было бы делать запрос средств у других пользователей, как это сделано в Swedbank. А так все очень нравится.</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>Edimaks</t>
+          <t>bsmayuki</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -9175,17 +9175,17 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>2020-03-19T11:06:32-07:00</t>
+          <t>2020-03-11T11:38:35-07:00</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>5683196586</t>
+          <t>5646994334</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id275598331</t>
+          <t>https://itunes.apple.com/lv/reviews/id982675283</t>
         </is>
       </c>
       <c r="K164" s="2" t="n">
@@ -9204,41 +9204,42 @@
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>9/10</t>
+          <t>Not great, not terrible</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>Очень крутой банк. Было бы идеально, если можно было бы делать запрос средств у других пользователей, как это сделано в Swedbank. А так все очень нравится.</t>
+          <t>Все очень красиво и летает вообще, но последняя версия на iPhone XR вообще не работает ничего, что связано с камерой - сначала хотела заказать карту через верификацию через приложение, камера вечно вылетала. Ок, пошла в филиал, где прождала 1,5 часа, чтоб заказать карту. 
+Там начался маразм с подключением mobile scan, который так же на моем телефоне не пошёл. В общем, карта - красота, бонусы прикольные, задумка класс, но баги и потеря 1,5 часов в филиале (очередь 5 человек была)) - просто выбесили в край</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>bsmayuki</t>
+          <t>nicole.an.moroz</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>12.21</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>2020-03-11T11:38:35-07:00</t>
+          <t>2020-01-04T00:50:14-07:00</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>5646994334</t>
+          <t>5358957913</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id982675283</t>
+          <t>https://itunes.apple.com/lv/reviews/id882642375</t>
         </is>
       </c>
       <c r="K165" s="2" t="n">
@@ -9257,42 +9258,41 @@
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Not great, not terrible</t>
+          <t>Apple Pay?</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>Все очень красиво и летает вообще, но последняя версия на iPhone XR вообще не работает ничего, что связано с камерой - сначала хотела заказать карту через верификацию через приложение, камера вечно вылетала. Ок, пошла в филиал, где прождала 1,5 часа, чтоб заказать карту. 
-Там начался маразм с подключением mobile scan, который так же на моем телефоне не пошёл. В общем, карта - красота, бонусы прикольные, задумка класс, но баги и потеря 1,5 часов в филиале (очередь 5 человек была)) - просто выбесили в край</t>
+          <t>Viss patīk! Bet kad parādīsies Apple Pay?</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>nicole.an.moroz</t>
+          <t>Alalambda</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>12.21</t>
+          <t>12.16</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>2020-01-04T00:50:14-07:00</t>
+          <t>2019-07-04T12:41:56-07:00</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>5358957913</t>
+          <t>4410970407</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id882642375</t>
+          <t>https://itunes.apple.com/lv/reviews/id573554755</t>
         </is>
       </c>
       <c r="K166" s="2" t="n">
@@ -9311,41 +9311,41 @@
         </is>
       </c>
       <c r="C167" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>Apple Pay?</t>
+          <t>Aplikācijas paziņojumi</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>Viss patīk! Bet kad parādīsies Apple Pay?</t>
+          <t>Viss ir labi, izņemot, ka no aplikàcijas nenāk paziņojumi par ienākošajiem darījumiem. Par izejošiem un kartes maksājumiem nāk paziņojumi.</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>Alalambda</t>
+          <t>Anne Bosix</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>12.16</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>2019-07-04T12:41:56-07:00</t>
+          <t>2019-06-09T01:56:56-07:00</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>4410970407</t>
+          <t>4288163184</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id573554755</t>
+          <t>https://itunes.apple.com/lv/reviews/id544683864</t>
         </is>
       </c>
       <c r="K167" s="2" t="n">
@@ -9364,21 +9364,21 @@
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>Aplikācijas paziņojumi</t>
+          <t>Eugene</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>Viss ir labi, izņemot, ka no aplikàcijas nenāk paziņojumi par ienākošajiem darījumiem. Par izejošiem un kartes maksājumiem nāk paziņojumi.</t>
+          <t>Loti laba aplikacija</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>Anne Bosix</t>
+          <t>jevgis2005</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
@@ -9388,17 +9388,17 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>2019-06-09T01:56:56-07:00</t>
+          <t>2019-05-05T15:23:45-07:00</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>4288163184</t>
+          <t>4106376133</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id544683864</t>
+          <t>https://itunes.apple.com/lv/reviews/id605202035</t>
         </is>
       </c>
       <c r="K168" s="2" t="n">
@@ -9421,17 +9421,17 @@
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>Eugene</t>
+          <t>Apple pay</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>Loti laba aplikacija</t>
+          <t>Все в приложении утраивает и работает хорошо, только одно НО: когда в iOS версии приложения добавите функцию «оплата телефоном», как на андроид?</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>jevgis2005</t>
+          <t>matrenababayan</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -9441,17 +9441,17 @@
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>2019-05-05T15:23:45-07:00</t>
+          <t>2019-04-20T11:21:28-07:00</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>4106376133</t>
+          <t>4038414103</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id605202035</t>
+          <t>https://itunes.apple.com/lv/reviews/id571383579</t>
         </is>
       </c>
       <c r="K169" s="2" t="n">
@@ -9474,17 +9474,17 @@
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>Apple pay</t>
+          <t>Fintech bank</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>Все в приложении утраивает и работает хорошо, только одно НО: когда в iOS версии приложения добавите функцию «оплата телефоном», как на андроид?</t>
+          <t>After the last update a bank app become my favourite banking app and even better then Revolute which for me was replaced by Citadele. Bank has a great transformation to become a main bank for me and my family! Congrats and good luck!</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>matrenababayan</t>
+          <t>markomalta</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -9494,17 +9494,17 @@
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>2019-04-20T11:21:28-07:00</t>
+          <t>2019-04-07T02:56:40-07:00</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>4038414103</t>
+          <t>3981495459</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id571383579</t>
+          <t>https://itunes.apple.com/lv/reviews/id563483440</t>
         </is>
       </c>
       <c r="K170" s="2" t="n">
@@ -9523,41 +9523,41 @@
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>Fintech bank</t>
+          <t>Необходимо улучшение</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>After the last update a bank app become my favourite banking app and even better then Revolute which for me was replaced by Citadele. Bank has a great transformation to become a main bank for me and my family! Congrats and good luck!</t>
+          <t>Приложение очень удобное и хорошее. Только не всегда работает. Периодически невозможно войти, не даёт возможности ввести логин и пароль.</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>markomalta</t>
+          <t>АлВерб</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>2019-04-07T02:56:40-07:00</t>
+          <t>2019-03-12T00:19:48-07:00</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>3981495459</t>
+          <t>3872074938</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id563483440</t>
+          <t>https://itunes.apple.com/lv/reviews/id736046138</t>
         </is>
       </c>
       <c r="K171" s="2" t="n">
@@ -9576,41 +9576,41 @@
         </is>
       </c>
       <c r="C172" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>Необходимо улучшение</t>
+          <t>Lieliska aplikācija</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>Приложение очень удобное и хорошее. Только не всегда работает. Периодически невозможно войти, не даёт возможности ввести логин и пароль.</t>
+          <t>Noderīgas notifikācijas par kontā veiktajiem darījumiem. Vēl gribētos iespēju saņemt notifikāciju arī, piemēram, par konta atlikumu, kurš zemāks par lietotāja noteiktu summu.</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>АлВерб</t>
+          <t>Oskars_M</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>12.12</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>2019-03-12T00:19:48-07:00</t>
+          <t>2019-02-16T08:51:51-07:00</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>3872074938</t>
+          <t>3777232492</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id736046138</t>
+          <t>https://itunes.apple.com/lv/reviews/id158131382</t>
         </is>
       </c>
       <c r="K172" s="2" t="n">
@@ -9633,17 +9633,17 @@
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>Lieliska aplikācija</t>
+          <t>Great App</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Noderīgas notifikācijas par kontā veiktajiem darījumiem. Vēl gribētos iespēju saņemt notifikāciju arī, piemēram, par konta atlikumu, kurš zemāks par lietotāja noteiktu summu.</t>
+          <t>Great user interface and easy to use better than other banks</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>Oskars_M</t>
+          <t>Dreamchaser56</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
@@ -9653,17 +9653,17 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>2019-02-16T08:51:51-07:00</t>
+          <t>2019-02-01T14:35:12-07:00</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>3777232492</t>
+          <t>3721870028</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id158131382</t>
+          <t>https://itunes.apple.com/lv/reviews/id649185568</t>
         </is>
       </c>
       <c r="K173" s="2" t="n">
@@ -9682,41 +9682,41 @@
         </is>
       </c>
       <c r="C174" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>Great App</t>
+          <t>🙁 3D touch atlikums</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>Great user interface and easy to use better than other banks</t>
+          <t>Līdz šim aplikācija ļoti patika. Pēc jaunā update absolūti nepatīk tas, ka lietojot 3D touch uz iPhone, lai apskatītu atlikumu, parādās divas summas un īstā no tām, kas ir pieejama, parādās, kā otrā maziem cipariem. Tas ir ļoti neērti, iepriekš rādījās tikai viena summa, tā, kura patiešām ir pieejama. Bija viegli un ērti pārskatāma. Vēlos, lai šis tiktu labots. Pārējais aplikācijā ir ērti un pārdomāti.</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>Dreamchaser56</t>
+          <t>Apolons Magiskais</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>12.12</t>
+          <t>12.11</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>2019-02-01T14:35:12-07:00</t>
+          <t>2019-01-04T12:17:42-07:00</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>3721870028</t>
+          <t>3612357272</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id649185568</t>
+          <t>https://itunes.apple.com/lv/reviews/id270878082</t>
         </is>
       </c>
       <c r="K174" s="2" t="n">
@@ -9735,41 +9735,41 @@
         </is>
       </c>
       <c r="C175" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>🙁 3D touch atlikums</t>
+          <t>Nestrādā apmaksa caur svītrukodu skenēšanu</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>Līdz šim aplikācija ļoti patika. Pēc jaunā update absolūti nepatīk tas, ka lietojot 3D touch uz iPhone, lai apskatītu atlikumu, parādās divas summas un īstā no tām, kas ir pieejama, parādās, kā otrā maziem cipariem. Tas ir ļoti neērti, iepriekš rādījās tikai viena summa, tā, kura patiešām ir pieejama. Bija viegli un ērti pārskatāma. Vēlos, lai šis tiktu labots. Pārējais aplikācijā ir ērti un pārdomāti.</t>
+          <t>Labdien, gribēju apmaksāt rēķinu ar kameru, bet pamēģināju un rada ka svītru kodi nav atrasti un kamera “salauzijas”. Paņemu otro iPhone , atjaunināju līdz 12.10 versijai un tāds pats. Lūgums salabojiet to.</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>Apolons Magiskais</t>
+          <t>LV1137</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.10</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>2019-01-04T12:17:42-07:00</t>
+          <t>2018-12-12T09:02:26-07:00</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>3612357272</t>
+          <t>3523219697</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id270878082</t>
+          <t>https://itunes.apple.com/lv/reviews/id637514913</t>
         </is>
       </c>
       <c r="K175" s="2" t="n">
@@ -9788,41 +9788,41 @@
         </is>
       </c>
       <c r="C176" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>Nestrādā apmaksa caur svītrukodu skenēšanu</t>
+          <t>Вопрос</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>Labdien, gribēju apmaksāt rēķinu ar kameru, bet pamēģināju un rada ka svītru kodi nav atrasti un kamera “salauzijas”. Paņemu otro iPhone , atjaunināju līdz 12.10 versijai un tāds pats. Lūgums salabojiet to.</t>
+          <t>С недавнего времени в строчке сумма к оплате не могу поставить запятую или точку между цифрами. Только если сначала 0. Например, мне надо перечислить 75 центов, тогда я могу написать 0.75, а вот если 1 евро и 75 центов, получается 175, т.к. после 1 не ставится точка. Что это вдруг?</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>LV1137</t>
+          <t>oxiol</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>12.10</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>2018-12-12T09:02:26-07:00</t>
+          <t>2018-10-25T14:17:03-07:00</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>3523219697</t>
+          <t>3343414722</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id637514913</t>
+          <t>https://itunes.apple.com/lv/reviews/id629199035</t>
         </is>
       </c>
       <c r="K176" s="2" t="n">
@@ -9841,21 +9841,21 @@
         </is>
       </c>
       <c r="C177" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>Вопрос</t>
+          <t>Pirktu nospiedums</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>С недавнего времени в строчке сумма к оплате не могу поставить запятую или точку между цифрами. Только если сначала 0. Например, мне надо перечислить 75 центов, тогда я могу написать 0.75, а вот если 1 евро и 75 центов, получается 175, т.к. после 1 не ставится точка. Что это вдруг?</t>
+          <t>Nestrādā pirkstu nospiedumu funkcija uz iphone 8plus un atrais atlikums arī visu laiku met arā un prasa no jauna autorizēties</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>oxiol</t>
+          <t>Kate281</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
@@ -9865,17 +9865,17 @@
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>2018-10-25T14:17:03-07:00</t>
+          <t>2018-10-23T06:08:02-07:00</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>3343414722</t>
+          <t>3334564495</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id629199035</t>
+          <t>https://itunes.apple.com/lv/reviews/id856240720</t>
         </is>
       </c>
       <c r="K177" s="2" t="n">
@@ -9894,76 +9894,77 @@
         </is>
       </c>
       <c r="C178" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>Pirktu nospiedums</t>
+          <t>Laba iBanka</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
-        <is>
-          <t>Nestrādā pirkstu nospiedumu funkcija uz iphone 8plus un atrais atlikums arī visu laiku met arā un prasa no jauna autorizēties</t>
-        </is>
-      </c>
-      <c r="F178" s="2" t="inlineStr">
-        <is>
-          <t>Kate281</t>
-        </is>
-      </c>
-      <c r="G178" s="2" t="inlineStr">
-        <is>
-          <t>12.9</t>
-        </is>
-      </c>
-      <c r="H178" s="2" t="inlineStr">
-        <is>
-          <t>2018-10-23T06:08:02-07:00</t>
-        </is>
-      </c>
-      <c r="I178" s="2" t="inlineStr">
-        <is>
-          <t>3334564495</t>
-        </is>
-      </c>
-      <c r="J178" s="2" t="inlineStr">
-        <is>
-          <t>https://itunes.apple.com/lv/reviews/id856240720</t>
-        </is>
-      </c>
-      <c r="K178" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
-        <is>
-          <t>Latvia</t>
-        </is>
-      </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>lv</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D179" s="3" t="inlineStr">
-        <is>
-          <t>Laba iBanka</t>
-        </is>
-      </c>
-      <c r="E179" s="3" t="inlineStr">
         <is>
           <t>Kopumā — lieliska aplikācija!
 Tomēr, personīgi, atklāšanas animācija ir kaitinoša un nedaudz par garu.
 Paziņojumi par jauniem ziņojumiem, t.i., mazais sarkanais punkts augšējā kreisajā stūrī, ir grūti pamanāmi. Es izmantoju aplikāciju vairākas reizes šajā mēnesī, bet pamanīju paziņojumu par jaunu ziņojumu, pusi mēnesi kopš tā ierašanās.</t>
         </is>
       </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Ervins Strauhmanis</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>2018-10-17T22:53:52-07:00</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>3314594358</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>https://itunes.apple.com/lv/reviews/id213491600</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>lv</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>Удалил новую версию</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>Разработчики забыли, что еще существуют люди с айфонами 5S и SE. После редизайна в новой версии все такое маленькое! Клавиатура для ввода PIN-кода теперь высотой в пол-экрана, по кнопкам еле попадаю, а раньше было на весь экран. И еще я хочу, чтобы мне перестало предлагать создать «код для быстрого входа» в интернет-банк, я не хочу, это небезопасно!
+В общем, буду сидеть на предыдущей версии, пока её не отключат</t>
+        </is>
+      </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>Ervins Strauhmanis</t>
+          <t>Fromlvbutliveuk</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
@@ -9973,17 +9974,17 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>2018-10-17T22:53:52-07:00</t>
+          <t>2018-08-31T00:15:05-07:00</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>3314594358</t>
+          <t>3135944159</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id213491600</t>
+          <t>https://itunes.apple.com/lv/reviews/id210964260</t>
         </is>
       </c>
       <c r="K179" s="2" t="n">
@@ -10002,42 +10003,41 @@
         </is>
       </c>
       <c r="C180" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>Удалил новую версию</t>
+          <t>Slikti</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>Разработчики забыли, что еще существуют люди с айфонами 5S и SE. После редизайна в новой версии все такое маленькое! Клавиатура для ввода PIN-кода теперь высотой в пол-экрана, по кнопкам еле попадаю, а раньше было на весь экран. И еще я хочу, чтобы мне перестало предлагать создать «код для быстрого входа» в интернет-банк, я не хочу, это небезопасно!
-В общем, буду сидеть на предыдущей версии, пока её не отключат</t>
+          <t>Kad varēs pieslēgties gan privātam, gan uzņēmuma kontam??</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>Fromlvbutliveuk</t>
+          <t>MartinsMartinš</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>2018-08-31T00:15:05-07:00</t>
+          <t>2018-07-27T12:28:58-07:00</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>3135944159</t>
+          <t>2979042093</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id210964260</t>
+          <t>https://itunes.apple.com/lv/reviews/id530429577</t>
         </is>
       </c>
       <c r="K180" s="2" t="n">
@@ -10056,41 +10056,41 @@
         </is>
       </c>
       <c r="C181" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>Slikti</t>
+          <t>Пинкод</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>Kad varēs pieslēgties gan privātam, gan uzņēmuma kontam??</t>
+          <t>Обновление возможно и хорошее. Но теперь не зайти и платёж не подтвердить - пинкод был 4 цифры а теперь спрашивает пять.</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>MartinsMartinš</t>
+          <t>Daarh</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>2018-07-27T12:28:58-07:00</t>
+          <t>2018-07-17T12:14:08-07:00</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>2979042093</t>
+          <t>2925229088</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id530429577</t>
+          <t>https://itunes.apple.com/lv/reviews/id107165992</t>
         </is>
       </c>
       <c r="K181" s="2" t="n">
@@ -10109,21 +10109,22 @@
         </is>
       </c>
       <c r="C182" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>Пинкод</t>
+          <t>Системная ошибка</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>Обновление возможно и хорошее. Но теперь не зайти и платёж не подтвердить - пинкод был 4 цифры а теперь спрашивает пять.</t>
+          <t>Обновление приложения выглядит отлично, но зайти в интернет-банк не получается. После ввода всех данных появляется сообщение «системная ошибка» и так уже несколько дней. Постоянно пользуюсь интернет-банком, приходится заходить через браузер.
+UPD служба поддержки быстро отреагировала и выпустила обновление. Двойной респект!</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>Daarh</t>
+          <t>Daria_grig</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -10133,17 +10134,17 @@
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>2018-07-17T12:14:08-07:00</t>
+          <t>2018-07-13T10:21:01-07:00</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>2925229088</t>
+          <t>2901274096</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id107165992</t>
+          <t>https://itunes.apple.com/lv/reviews/id139936593</t>
         </is>
       </c>
       <c r="K182" s="2" t="n">
@@ -10166,38 +10167,37 @@
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>Системная ошибка</t>
+          <t>Izcili</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>Обновление приложения выглядит отлично, но зайти в интернет-банк не получается. После ввода всех данных появляется сообщение «системная ошибка» и так уже несколько дней. Постоянно пользуюсь интернет-банком, приходится заходить через браузер.
-UPD служба поддержки быстро отреагировала и выпустила обновление. Двойной респект!</t>
+          <t>Izcila jaunā versija - TouchID/FaceID, ērti lietot, ļoti ātra, viss perfekti</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>Daria_grig</t>
+          <t>maxisfromea</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>2018-07-13T10:21:01-07:00</t>
+          <t>2018-06-20T01:51:21-07:00</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>2901274096</t>
+          <t>2730077901</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id139936593</t>
+          <t>https://itunes.apple.com/lv/reviews/id312405781</t>
         </is>
       </c>
       <c r="K183" s="2" t="n">
@@ -10216,41 +10216,41 @@
         </is>
       </c>
       <c r="C184" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>Izcili</t>
+          <t>Новая бета версия апликации</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>Izcila jaunā versija - TouchID/FaceID, ērti lietot, ļoti ātra, viss perfekti</t>
+          <t>Здравствуйте! Участвую в бета тестировании приложения, все круто, но кнопки внизу приложения ужасные, замените на что то более красивое)</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>maxisfromea</t>
+          <t>Alexdxc_s</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>2018-06-20T01:51:21-07:00</t>
+          <t>2018-05-23T15:25:13-07:00</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>2730077901</t>
+          <t>2586972053</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id312405781</t>
+          <t>https://itunes.apple.com/lv/reviews/id632944192</t>
         </is>
       </c>
       <c r="K184" s="2" t="n">
@@ -10269,41 +10269,41 @@
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>Новая бета версия апликации</t>
+          <t>Everything is fine, but..</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Здравствуйте! Участвую в бета тестировании приложения, все круто, но кнопки внизу приложения ужасные, замените на что то более красивое)</t>
+          <t>It would be much much better to use Touch-ID or Face-ID rather than PIN.</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>Alexdxc_s</t>
+          <t>Viktor Daskevics</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>2018-05-23T15:25:13-07:00</t>
+          <t>2017-11-09T23:30:34-07:00</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>2586972053</t>
+          <t>1910209750</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id632944192</t>
+          <t>https://itunes.apple.com/lv/reviews/id306228328</t>
         </is>
       </c>
       <c r="K185" s="2" t="n">
@@ -10322,41 +10322,41 @@
         </is>
       </c>
       <c r="C186" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Everything is fine, but..</t>
+          <t>iPad</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>It would be much much better to use Touch-ID or Face-ID rather than PIN.</t>
+          <t>Kad sagaidāma priekš iPad optimizēta versija?</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>Viktor Daskevics</t>
+          <t>MacPhisto..</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>2017-11-09T23:30:34-07:00</t>
+          <t>2017-06-15T10:57:34-07:00</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>1910209750</t>
+          <t>1645483609</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id306228328</t>
+          <t>https://itunes.apple.com/lv/reviews/id24310749</t>
         </is>
       </c>
       <c r="K186" s="2" t="n">
@@ -10375,21 +10375,22 @@
         </is>
       </c>
       <c r="C187" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>iPad</t>
+          <t>Widget</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Kad sagaidāma priekš iPad optimizēta versija?</t>
+          <t>Unable to load
+Update: Pēc ātrā atlikuma atslēgšanas un pieslēgšanas atpakaļ widģets sāka darboties kā nākas .</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>MacPhisto..</t>
+          <t>kadrsLV</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
@@ -10399,17 +10400,17 @@
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>2017-06-15T10:57:34-07:00</t>
+          <t>2017-06-08T11:13:46-07:00</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>1645483609</t>
+          <t>1637779518</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id24310749</t>
+          <t>https://itunes.apple.com/lv/reviews/id535925055</t>
         </is>
       </c>
       <c r="K187" s="2" t="n">
@@ -10428,22 +10429,21 @@
         </is>
       </c>
       <c r="C188" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Widget</t>
+          <t>kas te?</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>Unable to load
-Update: Pēc ātrā atlikuma atslēgšanas un pieslēgšanas atpakaļ widģets sāka darboties kā nākas .</t>
+          <t>vidzets vel projam nedarbojas ar iphone 7 (iOS 10.3.2)</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>kadrsLV</t>
+          <t>xheets</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -10453,17 +10453,17 @@
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>2017-06-08T11:13:46-07:00</t>
+          <t>2017-05-27T05:20:09-07:00</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>1637779518</t>
+          <t>1625696152</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id535925055</t>
+          <t>https://itunes.apple.com/lv/reviews/id552699107</t>
         </is>
       </c>
       <c r="K188" s="2" t="n">
@@ -10482,41 +10482,41 @@
         </is>
       </c>
       <c r="C189" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>kas te?</t>
+          <t>👍🏻</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>vidzets vel projam nedarbojas ar iphone 7 (iOS 10.3.2)</t>
+          <t>Labākā pieejamā mobilā aplikācija šobrīd, bez atsevišķas ierēces, lai ielogotos 👍🏻</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>xheets</t>
+          <t>Baiba83</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>2017-05-27T05:20:09-07:00</t>
+          <t>2017-01-21T04:41:11-07:00</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>1625696152</t>
+          <t>1527217295</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id552699107</t>
+          <t>https://itunes.apple.com/lv/reviews/id253411074</t>
         </is>
       </c>
       <c r="K189" s="2" t="n">
@@ -10539,37 +10539,37 @@
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>👍🏻</t>
+          <t>Izcili</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>Labākā pieejamā mobilā aplikācija šobrīd, bez atsevišķas ierēces, lai ielogotos 👍🏻</t>
+          <t>Labākais internet banking Latvijā, gaidam Touch ID atbalstu :)</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>Baiba83</t>
+          <t>Alohabandora</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>2017-01-21T04:41:11-07:00</t>
+          <t>2017-01-03T23:34:54-07:00</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>1527217295</t>
+          <t>1515007014</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id253411074</t>
+          <t>https://itunes.apple.com/lv/reviews/id318702180</t>
         </is>
       </c>
       <c r="K190" s="2" t="n">
@@ -10592,37 +10592,37 @@
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>Izcili</t>
+          <t>Super</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>Labākais internet banking Latvijā, gaidam Touch ID atbalstu :)</t>
+          <t>Viss labi strādā</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
-          <t>Alohabandora</t>
+          <t>Shdirieie</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>2017-01-03T23:34:54-07:00</t>
+          <t>2016-12-02T04:24:36-07:00</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>1515007014</t>
+          <t>1494578312</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id318702180</t>
+          <t>https://itunes.apple.com/lv/reviews/id390500416</t>
         </is>
       </c>
       <c r="K191" s="2" t="n">
@@ -10641,41 +10641,41 @@
         </is>
       </c>
       <c r="C192" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Super</t>
+          <t>👍🏽👎🏽</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>Viss labi strādā</t>
+          <t>Kapēc nevar saglabat šablonus?</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>Shdirieie</t>
+          <t>MusicBoy1313</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>2016-12-02T04:24:36-07:00</t>
+          <t>2016-05-23T12:07:28-07:00</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>1494578312</t>
+          <t>1383061280</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id390500416</t>
+          <t>https://itunes.apple.com/lv/reviews/id453813081</t>
         </is>
       </c>
       <c r="K192" s="2" t="n">
@@ -10694,21 +10694,21 @@
         </is>
       </c>
       <c r="C193" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>👍🏽👎🏽</t>
+          <t>Lieliski!</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>Kapēc nevar saglabat šablonus?</t>
+          <t>Tā turpināt!</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>MusicBoy1313</t>
+          <t>Pjanka</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
@@ -10718,17 +10718,17 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>2016-05-23T12:07:28-07:00</t>
+          <t>2016-04-20T12:14:05-07:00</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>1383061280</t>
+          <t>1366253873</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id453813081</t>
+          <t>https://itunes.apple.com/lv/reviews/id87664347</t>
         </is>
       </c>
       <c r="K193" s="2" t="n">
@@ -10751,17 +10751,18 @@
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>Lieliski!</t>
+          <t>lieliski</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>Tā turpināt!</t>
+          <t>ļoti ērta
+un kona atlikums bez autorizacijas, super</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>Pjanka</t>
+          <t>reiniiz</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
@@ -10771,17 +10772,17 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>2016-04-20T12:14:05-07:00</t>
+          <t>2016-04-20T00:05:12-07:00</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>1366253873</t>
+          <t>1366022003</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id87664347</t>
+          <t>https://itunes.apple.com/lv/reviews/id162755556</t>
         </is>
       </c>
       <c r="K194" s="2" t="n">
@@ -10804,18 +10805,17 @@
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>lieliski</t>
+          <t>Спасибо</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>ļoti ērta
-un kona atlikums bez autorizacijas, super</t>
+          <t>Спасибо что заботитесь о своих клиентах!</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>reiniiz</t>
+          <t>Diana.ru</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
@@ -10825,17 +10825,17 @@
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>2016-04-20T00:05:12-07:00</t>
+          <t>2016-04-19T22:49:17-07:00</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>1366022003</t>
+          <t>1365999192</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id162755556</t>
+          <t>https://itunes.apple.com/lv/reviews/id226777136</t>
         </is>
       </c>
       <c r="K195" s="2" t="n">
@@ -10854,41 +10854,41 @@
         </is>
       </c>
       <c r="C196" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Спасибо</t>
+          <t>Very bad app.</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>Спасибо что заботитесь о своих клиентах!</t>
+          <t>Opening app-it is in russina language no possibility to change it only when you are logged in you hve this option. And when I was trying to make a payment it didn't allow to scroll down and finish payment. So better use web version.</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>Diana.ru</t>
+          <t>Linda-del13</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>2016-04-19T22:49:17-07:00</t>
+          <t>2015-03-08T03:32:04-07:00</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>1365999192</t>
+          <t>1165152843</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id226777136</t>
+          <t>https://itunes.apple.com/lv/reviews/id223231931</t>
         </is>
       </c>
       <c r="K196" s="2" t="n">
@@ -10911,17 +10911,17 @@
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>Very bad app.</t>
+          <t>Когда?</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>Opening app-it is in russina language no possibility to change it only when you are logged in you hve this option. And when I was trying to make a payment it didn't allow to scroll down and finish payment. So better use web version.</t>
+          <t>Ёлы-палы, когда уже разработчики сделают функцию "быстрого остатка"? Как, например, у Swedbank. А цифровую клавиатуру вызвать при запросе ЦИФРОВОГО кода слабо? Очень слабое приложение!</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>Linda-del13</t>
+          <t>serfree</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
@@ -10931,17 +10931,17 @@
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>2015-03-08T03:32:04-07:00</t>
+          <t>2015-02-13T14:25:09-07:00</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>1165152843</t>
+          <t>1147530416</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id223231931</t>
+          <t>https://itunes.apple.com/lv/reviews/id210060829</t>
         </is>
       </c>
       <c r="K197" s="2" t="n">
@@ -10960,41 +10960,41 @@
         </is>
       </c>
       <c r="C198" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Когда?</t>
+          <t>Qiwi</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>Ёлы-палы, когда уже разработчики сделают функцию "быстрого остатка"? Как, например, у Swedbank. А цифровую клавиатуру вызвать при запросе ЦИФРОВОГО кода слабо? Очень слабое приложение!</t>
+          <t>Nav iespējas veilt maksājumus...</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>serfree</t>
+          <t>s.galayev</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>2015-02-13T14:25:09-07:00</t>
+          <t>2014-12-11T23:42:14-07:00</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>1147530416</t>
+          <t>1111862532</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id210060829</t>
+          <t>https://itunes.apple.com/lv/reviews/id142059094</t>
         </is>
       </c>
       <c r="K198" s="2" t="n">
@@ -11013,21 +11013,21 @@
         </is>
       </c>
       <c r="C199" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>Qiwi</t>
+          <t>Premiumrent.lv</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>Nav iespējas veilt maksājumus...</t>
+          <t>Удобная в использование!</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>s.galayev</t>
+          <t>premiumrent.lv</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
@@ -11037,17 +11037,17 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>2014-12-11T23:42:14-07:00</t>
+          <t>2014-11-11T02:17:32-07:00</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>1111862532</t>
+          <t>1095232549</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id142059094</t>
+          <t>https://itunes.apple.com/lv/reviews/id378470830</t>
         </is>
       </c>
       <c r="K199" s="2" t="n">
@@ -11066,41 +11066,41 @@
         </is>
       </c>
       <c r="C200" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Premiumrent.lv</t>
+          <t>Labs!</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>Удобная в использование!</t>
+          <t>Tagad ta tiesam ir Mobila banka! Loti erta un funkcionala.</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>premiumrent.lv</t>
+          <t>Normunds R</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>2014-11-11T02:17:32-07:00</t>
+          <t>2013-02-05T12:56:53-07:00</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>1095232549</t>
+          <t>745077954</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id378470830</t>
+          <t>https://itunes.apple.com/lv/reviews/id288416864</t>
         </is>
       </c>
       <c r="K200" s="2" t="n">
@@ -11123,17 +11123,17 @@
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>Labs!</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>Tagad ta tiesam ir Mobila banka! Loti erta un funkcionala.</t>
+          <t>2.0 rules!</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>Normunds R</t>
+          <t>Svires</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
@@ -11143,17 +11143,17 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>2013-02-05T12:56:53-07:00</t>
+          <t>2013-02-04T11:55:44-07:00</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>745077954</t>
+          <t>744326020</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id288416864</t>
+          <t>https://itunes.apple.com/lv/reviews/id168350109</t>
         </is>
       </c>
       <c r="K201" s="2" t="n">
@@ -11172,41 +11172,41 @@
         </is>
       </c>
       <c r="C202" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Forsi</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>2.0 rules!</t>
+          <t>Kāda jēga no aplikācijas, ja internetbankā ar to ieiet nevar? Viss pārējais ir labi.</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>Svires</t>
+          <t>Lopelis</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>2013-02-04T11:55:44-07:00</t>
+          <t>2012-11-06T01:13:01-07:00</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>744326020</t>
+          <t>686450024</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id168350109</t>
+          <t>https://itunes.apple.com/lv/reviews/id86692157</t>
         </is>
       </c>
       <c r="K202" s="2" t="n">
@@ -11225,21 +11225,21 @@
         </is>
       </c>
       <c r="C203" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>Forsi</t>
+          <t>Курсы валют не актуализируются</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>Kāda jēga no aplikācijas, ja internetbankā ar to ieiet nevar? Viss pārējais ir labi.</t>
+          <t>Курсы валют не актуализируются, толку нет от такой информации</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>Lopelis</t>
+          <t>Alexxx777</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
@@ -11249,17 +11249,17 @@
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>2012-11-06T01:13:01-07:00</t>
+          <t>2012-04-28T22:13:08-07:00</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>686450024</t>
+          <t>573073991</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id86692157</t>
+          <t>https://itunes.apple.com/lv/reviews/id184854201</t>
         </is>
       </c>
       <c r="K203" s="2" t="n">
@@ -11282,17 +11282,17 @@
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>Курсы валют не актуализируются</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>Курсы валют не актуализируются, толку нет от такой информации</t>
+          <t>Программа класс, надо иметь каждому у кого счет в этом банке</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>Alexxx777</t>
+          <t>Maklim</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
@@ -11302,78 +11302,25 @@
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>2012-04-28T22:13:08-07:00</t>
+          <t>2012-04-16T05:08:10-07:00</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>573073991</t>
+          <t>564940384</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>https://itunes.apple.com/lv/reviews/id184854201</t>
+          <t>https://itunes.apple.com/lv/reviews/id230838062</t>
         </is>
       </c>
       <c r="K204" s="2" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
-        <is>
-          <t>Latvia</t>
-        </is>
-      </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t>lv</t>
-        </is>
-      </c>
-      <c r="C205" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D205" s="3" t="inlineStr">
-        <is>
-          <t>MK</t>
-        </is>
-      </c>
-      <c r="E205" s="3" t="inlineStr">
-        <is>
-          <t>Программа класс, надо иметь каждому у кого счет в этом банке</t>
-        </is>
-      </c>
-      <c r="F205" s="2" t="inlineStr">
-        <is>
-          <t>Maklim</t>
-        </is>
-      </c>
-      <c r="G205" s="2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="H205" s="2" t="inlineStr">
-        <is>
-          <t>2012-04-16T05:08:10-07:00</t>
-        </is>
-      </c>
-      <c r="I205" s="2" t="inlineStr">
-        <is>
-          <t>564940384</t>
-        </is>
-      </c>
-      <c r="J205" s="2" t="inlineStr">
-        <is>
-          <t>https://itunes.apple.com/lv/reviews/id230838062</t>
-        </is>
-      </c>
-      <c r="K205" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K205"/>
+  <autoFilter ref="A1:K204"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11555,7 +11502,7 @@
         <v/>
       </c>
       <c r="C5" s="7">
-        <f>IFERROR(AVERAGE(Reviews!C2:C205),0)</f>
+        <f>IFERROR(AVERAGE(Reviews!C2:C204),0)</f>
         <v/>
       </c>
       <c r="D5" s="6">
